--- a/argus/kship/models/217590_model.xlsx
+++ b/argus/kship/models/217590_model.xlsx
@@ -21,7 +21,7 @@
     <definedName name="변수H">변수!$C$1:$V$1</definedName>
     <definedName name="환율">변수!$C$6:$V$13</definedName>
     <definedName name="BS연결H">BS연결!$C$1:$V$1</definedName>
-    <definedName name="BS연결">BS연결!$C$5:$V$93</definedName>
+    <definedName name="BS연결">BS연결!$C$5:$V$102</definedName>
     <definedName name="BS별도H">BS별도!$C$1:$V$1</definedName>
     <definedName name="BS별도">BS별도!$C$5:$V$89</definedName>
     <definedName name="SUBQH">subQ!$A$1:$V$1</definedName>
@@ -3822,7 +3822,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-09-30</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-02</t>
         </is>
       </c>
     </row>
@@ -6890,7 +6890,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V93"/>
+  <dimension ref="A1:V102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -7032,7 +7032,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-09-30</t>
+          <t>UPDATE: 26-10-02</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -9804,21 +9804,12 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>영업활동으로인한현금흐름</t>
-        </is>
-      </c>
-      <c r="E76" s="18" t="n">
-        <v>3179.86</v>
-      </c>
-      <c r="F76" s="18" t="n">
-        <v>1701.41</v>
+          <t>이자수익</t>
+        </is>
       </c>
       <c r="G76" s="9" t="n"/>
-      <c r="H76" s="18" t="n">
-        <v>-11848.54</v>
-      </c>
       <c r="I76" s="19" t="n">
-        <v>-1220.13</v>
+        <v>233.78</v>
       </c>
       <c r="J76" s="10" t="n"/>
       <c r="K76" s="10" t="n"/>
@@ -9840,21 +9831,12 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>이자수취(CF)</t>
-        </is>
-      </c>
-      <c r="E77" s="18" t="n">
-        <v>464.21</v>
-      </c>
-      <c r="F77" s="18" t="n">
-        <v>229.89</v>
+          <t>이자비용</t>
+        </is>
       </c>
       <c r="G77" s="9" t="n"/>
-      <c r="H77" s="18" t="n">
-        <v>79.79000000000001</v>
-      </c>
       <c r="I77" s="19" t="n">
-        <v>283.24</v>
+        <v>598.17</v>
       </c>
       <c r="J77" s="10" t="n"/>
       <c r="K77" s="10" t="n"/>
@@ -9876,21 +9858,12 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>법인세납부(CF)</t>
-        </is>
-      </c>
-      <c r="E78" s="18" t="n">
-        <v>-463.69</v>
-      </c>
-      <c r="F78" s="18" t="n">
-        <v>-28.77</v>
+          <t>외환차익</t>
+        </is>
       </c>
       <c r="G78" s="9" t="n"/>
-      <c r="H78" s="18" t="n">
-        <v>-18.37</v>
-      </c>
       <c r="I78" s="19" t="n">
-        <v>-259.35</v>
+        <v>149.14</v>
       </c>
       <c r="J78" s="10" t="n"/>
       <c r="K78" s="10" t="n"/>
@@ -9912,21 +9885,12 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>투자활동으로인한현금흐름</t>
-        </is>
-      </c>
-      <c r="E79" s="18" t="n">
-        <v>16813.94</v>
-      </c>
-      <c r="F79" s="18" t="n">
-        <v>-28713.83</v>
+          <t>외환차손</t>
+        </is>
       </c>
       <c r="G79" s="9" t="n"/>
-      <c r="H79" s="18" t="n">
-        <v>8511.07</v>
-      </c>
       <c r="I79" s="19" t="n">
-        <v>9091.24</v>
+        <v>169.59</v>
       </c>
       <c r="J79" s="10" t="n"/>
       <c r="K79" s="10" t="n"/>
@@ -9948,17 +9912,13 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>무형자산의감소</t>
-        </is>
-      </c>
-      <c r="E80" s="18" t="n">
-        <v>100</v>
-      </c>
-      <c r="F80" s="18" t="n">
-        <v>0</v>
+          <t>외화환산이익</t>
+        </is>
       </c>
       <c r="G80" s="9" t="n"/>
-      <c r="I80" s="5" t="n"/>
+      <c r="I80" s="19" t="n">
+        <v>41.56</v>
+      </c>
       <c r="J80" s="10" t="n"/>
       <c r="K80" s="10" t="n"/>
       <c r="L80" s="11" t="n"/>
@@ -9979,21 +9939,12 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>유형자산의증가</t>
-        </is>
-      </c>
-      <c r="E81" s="18" t="n">
-        <v>736.35</v>
-      </c>
-      <c r="F81" s="18" t="n">
-        <v>208.8</v>
+          <t>외화환산손실</t>
+        </is>
       </c>
       <c r="G81" s="9" t="n"/>
-      <c r="H81" s="18" t="n">
-        <v>567.22</v>
-      </c>
       <c r="I81" s="19" t="n">
-        <v>817.3200000000001</v>
+        <v>-78.17</v>
       </c>
       <c r="J81" s="10" t="n"/>
       <c r="K81" s="10" t="n"/>
@@ -10015,21 +9966,12 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>CAPEX</t>
-        </is>
-      </c>
-      <c r="E82" s="18" t="n">
-        <v>2021.74</v>
-      </c>
-      <c r="F82" s="18" t="n">
-        <v>196.04</v>
+          <t>파생상품이익</t>
+        </is>
       </c>
       <c r="G82" s="9" t="n"/>
-      <c r="H82" s="18" t="n">
-        <v>610.92</v>
-      </c>
       <c r="I82" s="19" t="n">
-        <v>844.08</v>
+        <v>2834.04</v>
       </c>
       <c r="J82" s="10" t="n"/>
       <c r="K82" s="10" t="n"/>
@@ -10051,18 +9993,12 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>무형자산의증가</t>
-        </is>
-      </c>
-      <c r="E83" s="18" t="n">
-        <v>1285.39</v>
+          <t>파생상품손실</t>
+        </is>
       </c>
       <c r="G83" s="9" t="n"/>
-      <c r="H83" s="18" t="n">
-        <v>43.7</v>
-      </c>
       <c r="I83" s="19" t="n">
-        <v>26.76</v>
+        <v>1603.13</v>
       </c>
       <c r="J83" s="10" t="n"/>
       <c r="K83" s="10" t="n"/>
@@ -10084,21 +10020,12 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>재무활동으로인한현금흐름</t>
-        </is>
-      </c>
-      <c r="E84" s="18" t="n">
-        <v>-16850.22</v>
-      </c>
-      <c r="F84" s="18" t="n">
-        <v>32068.43</v>
+          <t>이자손익</t>
+        </is>
       </c>
       <c r="G84" s="9" t="n"/>
-      <c r="H84" s="18" t="n">
-        <v>-5311.51</v>
-      </c>
       <c r="I84" s="19" t="n">
-        <v>-6176.05</v>
+        <v>-364.39</v>
       </c>
       <c r="J84" s="10" t="n"/>
       <c r="K84" s="10" t="n"/>
@@ -10120,21 +10047,21 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>단기차입금의증가</t>
+          <t>영업활동으로인한현금흐름</t>
         </is>
       </c>
       <c r="E85" s="18" t="n">
-        <v>2357.49</v>
+        <v>3179.86</v>
       </c>
       <c r="F85" s="18" t="n">
-        <v>4679.08</v>
+        <v>1701.41</v>
       </c>
       <c r="G85" s="9" t="n"/>
       <c r="H85" s="18" t="n">
-        <v>22964.87</v>
+        <v>-11848.54</v>
       </c>
       <c r="I85" s="19" t="n">
-        <v>72936.17</v>
+        <v>-1220.13</v>
       </c>
       <c r="J85" s="10" t="n"/>
       <c r="K85" s="10" t="n"/>
@@ -10156,21 +10083,21 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>단기차입금의감소</t>
+          <t>이자수취(CF)</t>
         </is>
       </c>
       <c r="E86" s="18" t="n">
-        <v>4025.91</v>
+        <v>464.21</v>
       </c>
       <c r="F86" s="18" t="n">
-        <v>10388.44</v>
+        <v>229.89</v>
       </c>
       <c r="G86" s="9" t="n"/>
       <c r="H86" s="18" t="n">
-        <v>27287.15</v>
+        <v>79.79000000000001</v>
       </c>
       <c r="I86" s="19" t="n">
-        <v>76976.16</v>
+        <v>283.24</v>
       </c>
       <c r="J86" s="10" t="n"/>
       <c r="K86" s="10" t="n"/>
@@ -10192,21 +10119,21 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>유동성장기부채의감소</t>
+          <t>법인세납부(CF)</t>
         </is>
       </c>
       <c r="E87" s="18" t="n">
-        <v>195.65</v>
+        <v>-463.69</v>
       </c>
       <c r="F87" s="18" t="n">
-        <v>586.96</v>
+        <v>-28.77</v>
       </c>
       <c r="G87" s="9" t="n"/>
       <c r="H87" s="18" t="n">
-        <v>586.96</v>
+        <v>-18.37</v>
       </c>
       <c r="I87" s="19" t="n">
-        <v>586.95</v>
+        <v>-259.35</v>
       </c>
       <c r="J87" s="10" t="n"/>
       <c r="K87" s="10" t="n"/>
@@ -10228,17 +10155,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>사채의감소</t>
+          <t>투자활동으로인한현금흐름</t>
         </is>
       </c>
       <c r="E88" s="18" t="n">
-        <v>10500</v>
+        <v>16813.94</v>
       </c>
       <c r="F88" s="18" t="n">
-        <v>0</v>
+        <v>-28713.83</v>
       </c>
       <c r="G88" s="9" t="n"/>
-      <c r="I88" s="5" t="n"/>
+      <c r="H88" s="18" t="n">
+        <v>8511.07</v>
+      </c>
+      <c r="I88" s="19" t="n">
+        <v>9091.24</v>
+      </c>
       <c r="J88" s="10" t="n"/>
       <c r="K88" s="10" t="n"/>
       <c r="L88" s="11" t="n"/>
@@ -10259,22 +10191,17 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>현금및현금성자산의증감</t>
+          <t>무형자산의감소</t>
         </is>
       </c>
       <c r="E89" s="18" t="n">
-        <v>3143.58</v>
+        <v>100</v>
       </c>
       <c r="F89" s="18" t="n">
-        <v>5056.02</v>
+        <v>0</v>
       </c>
       <c r="G89" s="9" t="n"/>
-      <c r="H89" s="18" t="n">
-        <v>-8648.99</v>
-      </c>
-      <c r="I89" s="19" t="n">
-        <v>1695.07</v>
-      </c>
+      <c r="I89" s="5" t="n"/>
       <c r="J89" s="10" t="n"/>
       <c r="K89" s="10" t="n"/>
       <c r="L89" s="11" t="n"/>
@@ -10295,21 +10222,21 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>기말현금및현금성자산</t>
+          <t>유형자산의증가</t>
         </is>
       </c>
       <c r="E90" s="18" t="n">
-        <v>3218.76</v>
+        <v>736.35</v>
       </c>
       <c r="F90" s="18" t="n">
-        <v>4965.64</v>
+        <v>208.8</v>
       </c>
       <c r="G90" s="9" t="n"/>
       <c r="H90" s="18" t="n">
-        <v>1934.29</v>
+        <v>567.22</v>
       </c>
       <c r="I90" s="19" t="n">
-        <v>1670.48</v>
+        <v>817.3200000000001</v>
       </c>
       <c r="J90" s="10" t="n"/>
       <c r="K90" s="10" t="n"/>
@@ -10331,18 +10258,21 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>유형자산의감소</t>
-        </is>
+          <t>CAPEX</t>
+        </is>
+      </c>
+      <c r="E91" s="18" t="n">
+        <v>2021.74</v>
       </c>
       <c r="F91" s="18" t="n">
-        <v>109.7</v>
+        <v>196.04</v>
       </c>
       <c r="G91" s="9" t="n"/>
       <c r="H91" s="18" t="n">
-        <v>0</v>
+        <v>610.92</v>
       </c>
       <c r="I91" s="19" t="n">
-        <v>2.68</v>
+        <v>844.08</v>
       </c>
       <c r="J91" s="10" t="n"/>
       <c r="K91" s="10" t="n"/>
@@ -10364,14 +10294,19 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>장기차입금의증가</t>
-        </is>
-      </c>
-      <c r="F92" s="18" t="n">
-        <v>0</v>
+          <t>무형자산의증가</t>
+        </is>
+      </c>
+      <c r="E92" s="18" t="n">
+        <v>1285.39</v>
       </c>
       <c r="G92" s="9" t="n"/>
-      <c r="I92" s="5" t="n"/>
+      <c r="H92" s="18" t="n">
+        <v>43.7</v>
+      </c>
+      <c r="I92" s="19" t="n">
+        <v>26.76</v>
+      </c>
       <c r="J92" s="10" t="n"/>
       <c r="K92" s="10" t="n"/>
       <c r="L92" s="11" t="n"/>
@@ -10392,14 +10327,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>사채의증가</t>
-        </is>
+          <t>재무활동으로인한현금흐름</t>
+        </is>
+      </c>
+      <c r="E93" s="18" t="n">
+        <v>-16850.22</v>
       </c>
       <c r="F93" s="18" t="n">
-        <v>0</v>
+        <v>32068.43</v>
       </c>
       <c r="G93" s="9" t="n"/>
-      <c r="I93" s="5" t="n"/>
+      <c r="H93" s="18" t="n">
+        <v>-5311.51</v>
+      </c>
+      <c r="I93" s="19" t="n">
+        <v>-6176.05</v>
+      </c>
       <c r="J93" s="10" t="n"/>
       <c r="K93" s="10" t="n"/>
       <c r="L93" s="11" t="n"/>
@@ -10413,6 +10356,306 @@
       <c r="T93" s="10" t="n"/>
       <c r="U93" s="10" t="n"/>
       <c r="V93" s="11" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>1</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>단기차입금의증가</t>
+        </is>
+      </c>
+      <c r="E94" s="18" t="n">
+        <v>2357.49</v>
+      </c>
+      <c r="F94" s="18" t="n">
+        <v>4679.08</v>
+      </c>
+      <c r="G94" s="9" t="n"/>
+      <c r="H94" s="18" t="n">
+        <v>22964.87</v>
+      </c>
+      <c r="I94" s="19" t="n">
+        <v>72936.17</v>
+      </c>
+      <c r="J94" s="10" t="n"/>
+      <c r="K94" s="10" t="n"/>
+      <c r="L94" s="11" t="n"/>
+      <c r="M94" s="10" t="n"/>
+      <c r="N94" s="10" t="n"/>
+      <c r="O94" s="10" t="n"/>
+      <c r="P94" s="10" t="n"/>
+      <c r="Q94" s="11" t="n"/>
+      <c r="R94" s="10" t="n"/>
+      <c r="S94" s="10" t="n"/>
+      <c r="T94" s="10" t="n"/>
+      <c r="U94" s="10" t="n"/>
+      <c r="V94" s="11" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>1</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>단기차입금의감소</t>
+        </is>
+      </c>
+      <c r="E95" s="18" t="n">
+        <v>4025.91</v>
+      </c>
+      <c r="F95" s="18" t="n">
+        <v>10388.44</v>
+      </c>
+      <c r="G95" s="9" t="n"/>
+      <c r="H95" s="18" t="n">
+        <v>27287.15</v>
+      </c>
+      <c r="I95" s="19" t="n">
+        <v>76976.16</v>
+      </c>
+      <c r="J95" s="10" t="n"/>
+      <c r="K95" s="10" t="n"/>
+      <c r="L95" s="11" t="n"/>
+      <c r="M95" s="10" t="n"/>
+      <c r="N95" s="10" t="n"/>
+      <c r="O95" s="10" t="n"/>
+      <c r="P95" s="10" t="n"/>
+      <c r="Q95" s="11" t="n"/>
+      <c r="R95" s="10" t="n"/>
+      <c r="S95" s="10" t="n"/>
+      <c r="T95" s="10" t="n"/>
+      <c r="U95" s="10" t="n"/>
+      <c r="V95" s="11" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>1</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>유동성장기부채의감소</t>
+        </is>
+      </c>
+      <c r="E96" s="18" t="n">
+        <v>195.65</v>
+      </c>
+      <c r="F96" s="18" t="n">
+        <v>586.96</v>
+      </c>
+      <c r="G96" s="9" t="n"/>
+      <c r="H96" s="18" t="n">
+        <v>586.96</v>
+      </c>
+      <c r="I96" s="19" t="n">
+        <v>586.95</v>
+      </c>
+      <c r="J96" s="10" t="n"/>
+      <c r="K96" s="10" t="n"/>
+      <c r="L96" s="11" t="n"/>
+      <c r="M96" s="10" t="n"/>
+      <c r="N96" s="10" t="n"/>
+      <c r="O96" s="10" t="n"/>
+      <c r="P96" s="10" t="n"/>
+      <c r="Q96" s="11" t="n"/>
+      <c r="R96" s="10" t="n"/>
+      <c r="S96" s="10" t="n"/>
+      <c r="T96" s="10" t="n"/>
+      <c r="U96" s="10" t="n"/>
+      <c r="V96" s="11" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>1</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>사채의감소</t>
+        </is>
+      </c>
+      <c r="E97" s="18" t="n">
+        <v>10500</v>
+      </c>
+      <c r="F97" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G97" s="9" t="n"/>
+      <c r="I97" s="5" t="n"/>
+      <c r="J97" s="10" t="n"/>
+      <c r="K97" s="10" t="n"/>
+      <c r="L97" s="11" t="n"/>
+      <c r="M97" s="10" t="n"/>
+      <c r="N97" s="10" t="n"/>
+      <c r="O97" s="10" t="n"/>
+      <c r="P97" s="10" t="n"/>
+      <c r="Q97" s="11" t="n"/>
+      <c r="R97" s="10" t="n"/>
+      <c r="S97" s="10" t="n"/>
+      <c r="T97" s="10" t="n"/>
+      <c r="U97" s="10" t="n"/>
+      <c r="V97" s="11" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>1</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>현금및현금성자산의증감</t>
+        </is>
+      </c>
+      <c r="E98" s="18" t="n">
+        <v>3143.58</v>
+      </c>
+      <c r="F98" s="18" t="n">
+        <v>5056.02</v>
+      </c>
+      <c r="G98" s="9" t="n"/>
+      <c r="H98" s="18" t="n">
+        <v>-8648.99</v>
+      </c>
+      <c r="I98" s="19" t="n">
+        <v>1695.07</v>
+      </c>
+      <c r="J98" s="10" t="n"/>
+      <c r="K98" s="10" t="n"/>
+      <c r="L98" s="11" t="n"/>
+      <c r="M98" s="10" t="n"/>
+      <c r="N98" s="10" t="n"/>
+      <c r="O98" s="10" t="n"/>
+      <c r="P98" s="10" t="n"/>
+      <c r="Q98" s="11" t="n"/>
+      <c r="R98" s="10" t="n"/>
+      <c r="S98" s="10" t="n"/>
+      <c r="T98" s="10" t="n"/>
+      <c r="U98" s="10" t="n"/>
+      <c r="V98" s="11" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>1</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>기말현금및현금성자산</t>
+        </is>
+      </c>
+      <c r="E99" s="18" t="n">
+        <v>3218.76</v>
+      </c>
+      <c r="F99" s="18" t="n">
+        <v>4965.64</v>
+      </c>
+      <c r="G99" s="9" t="n"/>
+      <c r="H99" s="18" t="n">
+        <v>1934.29</v>
+      </c>
+      <c r="I99" s="19" t="n">
+        <v>1670.48</v>
+      </c>
+      <c r="J99" s="10" t="n"/>
+      <c r="K99" s="10" t="n"/>
+      <c r="L99" s="11" t="n"/>
+      <c r="M99" s="10" t="n"/>
+      <c r="N99" s="10" t="n"/>
+      <c r="O99" s="10" t="n"/>
+      <c r="P99" s="10" t="n"/>
+      <c r="Q99" s="11" t="n"/>
+      <c r="R99" s="10" t="n"/>
+      <c r="S99" s="10" t="n"/>
+      <c r="T99" s="10" t="n"/>
+      <c r="U99" s="10" t="n"/>
+      <c r="V99" s="11" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>1</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>유형자산의감소</t>
+        </is>
+      </c>
+      <c r="F100" s="18" t="n">
+        <v>109.7</v>
+      </c>
+      <c r="G100" s="9" t="n"/>
+      <c r="H100" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I100" s="19" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="J100" s="10" t="n"/>
+      <c r="K100" s="10" t="n"/>
+      <c r="L100" s="11" t="n"/>
+      <c r="M100" s="10" t="n"/>
+      <c r="N100" s="10" t="n"/>
+      <c r="O100" s="10" t="n"/>
+      <c r="P100" s="10" t="n"/>
+      <c r="Q100" s="11" t="n"/>
+      <c r="R100" s="10" t="n"/>
+      <c r="S100" s="10" t="n"/>
+      <c r="T100" s="10" t="n"/>
+      <c r="U100" s="10" t="n"/>
+      <c r="V100" s="11" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>1</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>장기차입금의증가</t>
+        </is>
+      </c>
+      <c r="F101" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G101" s="9" t="n"/>
+      <c r="I101" s="5" t="n"/>
+      <c r="J101" s="10" t="n"/>
+      <c r="K101" s="10" t="n"/>
+      <c r="L101" s="11" t="n"/>
+      <c r="M101" s="10" t="n"/>
+      <c r="N101" s="10" t="n"/>
+      <c r="O101" s="10" t="n"/>
+      <c r="P101" s="10" t="n"/>
+      <c r="Q101" s="11" t="n"/>
+      <c r="R101" s="10" t="n"/>
+      <c r="S101" s="10" t="n"/>
+      <c r="T101" s="10" t="n"/>
+      <c r="U101" s="10" t="n"/>
+      <c r="V101" s="11" t="n"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>1</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>사채의증가</t>
+        </is>
+      </c>
+      <c r="F102" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G102" s="9" t="n"/>
+      <c r="I102" s="5" t="n"/>
+      <c r="J102" s="10" t="n"/>
+      <c r="K102" s="10" t="n"/>
+      <c r="L102" s="11" t="n"/>
+      <c r="M102" s="10" t="n"/>
+      <c r="N102" s="10" t="n"/>
+      <c r="O102" s="10" t="n"/>
+      <c r="P102" s="10" t="n"/>
+      <c r="Q102" s="11" t="n"/>
+      <c r="R102" s="10" t="n"/>
+      <c r="S102" s="10" t="n"/>
+      <c r="T102" s="10" t="n"/>
+      <c r="U102" s="10" t="n"/>
+      <c r="V102" s="11" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10567,7 +10810,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-09-30</t>
+          <t>UPDATE: 26-10-02</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/217590_model.xlsx
+++ b/argus/kship/models/217590_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$V$1</definedName>
@@ -3989,7 +3989,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-05</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-06</t>
         </is>
       </c>
     </row>
@@ -4541,35 +4541,35 @@
         <v>1418.75</v>
       </c>
       <c r="K6" s="16" t="n">
-        <v>1354.78</v>
+        <v>1351.18</v>
       </c>
       <c r="L6" s="17" t="n">
-        <v>1460.21</v>
+        <v>1459.61</v>
       </c>
       <c r="M6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="N6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="O6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="P6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="Q6" s="11" t="n"/>
       <c r="R6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="S6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="T6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="U6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="V6" s="11" t="n"/>
     </row>
@@ -4603,35 +4603,35 @@
         <v>1355.4</v>
       </c>
       <c r="K7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="L7" s="17" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="M7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="N7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="O7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="P7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="Q7" s="11" t="n"/>
       <c r="R7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="S7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="T7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="U7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="V7" s="11" t="n"/>
     </row>
@@ -4665,35 +4665,35 @@
         <v>890.41</v>
       </c>
       <c r="K8" s="16" t="n">
-        <v>858.4</v>
+        <v>855.39</v>
       </c>
       <c r="L8" s="17" t="n">
-        <v>921.0599999999999</v>
+        <v>920.6900000000001</v>
       </c>
       <c r="M8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="N8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="O8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="P8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="Q8" s="11" t="n"/>
       <c r="R8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="S8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="T8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="U8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="V8" s="11" t="n"/>
     </row>
@@ -4727,35 +4727,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="K9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="L9" s="17" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="M9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="N9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="O9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="P9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="Q9" s="11" t="n"/>
       <c r="R9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="S9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="T9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="U9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="V9" s="11" t="n"/>
     </row>
@@ -4789,35 +4789,35 @@
         <v>1631.97</v>
       </c>
       <c r="K10" s="16" t="n">
-        <v>1525.7</v>
+        <v>1519.07</v>
       </c>
       <c r="L10" s="17" t="n">
-        <v>1694.79</v>
+        <v>1693.81</v>
       </c>
       <c r="M10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="N10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="O10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="P10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="Q10" s="11" t="n"/>
       <c r="R10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="S10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="T10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="U10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="V10" s="11" t="n"/>
     </row>
@@ -4851,35 +4851,35 @@
         <v>1539.06</v>
       </c>
       <c r="K11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="L11" s="17" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="M11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="N11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="O11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="P11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="Q11" s="11" t="n"/>
       <c r="R11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="S11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="T11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="U11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="V11" s="11" t="n"/>
     </row>
@@ -4913,35 +4913,35 @@
         <v>210.43</v>
       </c>
       <c r="K12" s="16" t="n">
-        <v>202.07</v>
+        <v>201.53</v>
       </c>
       <c r="L12" s="17" t="n">
-        <v>214.1</v>
+        <v>214.03</v>
       </c>
       <c r="M12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="N12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="O12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="P12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="Q12" s="11" t="n"/>
       <c r="R12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="S12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="T12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="U12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="V12" s="11" t="n"/>
     </row>
@@ -4975,35 +4975,35 @@
         <v>202.16</v>
       </c>
       <c r="K13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="L13" s="17" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="M13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="N13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="O13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="P13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="Q13" s="11" t="n"/>
       <c r="R13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="S13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="T13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="U13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="V13" s="11" t="n"/>
     </row>
@@ -5054,7 +5054,7 @@
         <v>13570</v>
       </c>
       <c r="K15" s="20" t="n">
-        <v>18440</v>
+        <v>19190</v>
       </c>
       <c r="L15" s="11" t="n"/>
       <c r="M15" s="10" t="n"/>
@@ -5093,7 +5093,7 @@
         <v>16170</v>
       </c>
       <c r="K16" s="20" t="n">
-        <v>18440</v>
+        <v>19570</v>
       </c>
       <c r="L16" s="11" t="n"/>
       <c r="M16" s="10" t="n"/>
@@ -5171,7 +5171,7 @@
         <v>12227.4</v>
       </c>
       <c r="K18" s="20" t="n">
-        <v>16330</v>
+        <v>17283.3</v>
       </c>
       <c r="L18" s="11" t="n"/>
       <c r="M18" s="10" t="n"/>
@@ -6708,7 +6708,7 @@
         </is>
       </c>
       <c r="D44" s="34" t="n">
-        <v>18440</v>
+        <v>19190</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
@@ -6744,7 +6744,7 @@
       </c>
       <c r="D45" s="35" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -7404,7 +7404,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-05</t>
+          <t>UPDATE: 26-10-06</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -11219,7 +11219,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-05</t>
+          <t>UPDATE: 26-10-06</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18341,7 +18341,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -21129,7 +21129,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E3" s="43" t="n">
@@ -22660,7 +22660,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>107.58</v>
+        <v>111.96</v>
       </c>
     </row>
     <row r="32">
@@ -22670,7 +22670,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>3.87</v>
+        <v>4.03</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/217590_model.xlsx
+++ b/argus/kship/models/217590_model.xlsx
@@ -3989,7 +3989,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-06</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-07</t>
         </is>
       </c>
     </row>
@@ -4541,35 +4541,35 @@
         <v>1418.75</v>
       </c>
       <c r="K6" s="16" t="n">
-        <v>1351.18</v>
+        <v>1348.08</v>
       </c>
       <c r="L6" s="17" t="n">
-        <v>1459.61</v>
+        <v>1458.99</v>
       </c>
       <c r="M6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="N6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="O6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="P6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="Q6" s="11" t="n"/>
       <c r="R6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="S6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="T6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="U6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="V6" s="11" t="n"/>
     </row>
@@ -4603,35 +4603,35 @@
         <v>1355.4</v>
       </c>
       <c r="K7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="L7" s="17" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="M7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="N7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="O7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="P7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="Q7" s="11" t="n"/>
       <c r="R7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="S7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="T7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="U7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="V7" s="11" t="n"/>
     </row>
@@ -4665,35 +4665,35 @@
         <v>890.41</v>
       </c>
       <c r="K8" s="16" t="n">
-        <v>855.39</v>
+        <v>853.26</v>
       </c>
       <c r="L8" s="17" t="n">
-        <v>920.6900000000001</v>
+        <v>920.3099999999999</v>
       </c>
       <c r="M8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="N8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="O8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="P8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="Q8" s="11" t="n"/>
       <c r="R8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="S8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="T8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="U8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="V8" s="11" t="n"/>
     </row>
@@ -4727,35 +4727,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="K9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="L9" s="17" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="M9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="N9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="O9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="P9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="Q9" s="11" t="n"/>
       <c r="R9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="S9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="T9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="U9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="V9" s="11" t="n"/>
     </row>
@@ -4789,35 +4789,35 @@
         <v>1631.97</v>
       </c>
       <c r="K10" s="16" t="n">
-        <v>1519.07</v>
+        <v>1516.47</v>
       </c>
       <c r="L10" s="17" t="n">
-        <v>1693.81</v>
+        <v>1692.86</v>
       </c>
       <c r="M10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="N10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="O10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="P10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="Q10" s="11" t="n"/>
       <c r="R10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="S10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="T10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="U10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="V10" s="11" t="n"/>
     </row>
@@ -4851,35 +4851,35 @@
         <v>1539.06</v>
       </c>
       <c r="K11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="L11" s="17" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="M11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="N11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="O11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="P11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="Q11" s="11" t="n"/>
       <c r="R11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="S11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="T11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="U11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="V11" s="11" t="n"/>
     </row>
@@ -4913,35 +4913,35 @@
         <v>210.43</v>
       </c>
       <c r="K12" s="16" t="n">
-        <v>201.53</v>
+        <v>201.07</v>
       </c>
       <c r="L12" s="17" t="n">
-        <v>214.03</v>
+        <v>213.96</v>
       </c>
       <c r="M12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="N12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="O12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="P12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="Q12" s="11" t="n"/>
       <c r="R12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="S12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="T12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="U12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="V12" s="11" t="n"/>
     </row>
@@ -4975,35 +4975,35 @@
         <v>202.16</v>
       </c>
       <c r="K13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="L13" s="17" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="M13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="N13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="O13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="P13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="Q13" s="11" t="n"/>
       <c r="R13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="S13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="T13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="U13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="V13" s="11" t="n"/>
     </row>
@@ -5054,7 +5054,7 @@
         <v>13570</v>
       </c>
       <c r="K15" s="20" t="n">
-        <v>19190</v>
+        <v>18730</v>
       </c>
       <c r="L15" s="11" t="n"/>
       <c r="M15" s="10" t="n"/>
@@ -5093,7 +5093,7 @@
         <v>16170</v>
       </c>
       <c r="K16" s="20" t="n">
-        <v>19570</v>
+        <v>20300</v>
       </c>
       <c r="L16" s="11" t="n"/>
       <c r="M16" s="10" t="n"/>
@@ -5171,7 +5171,7 @@
         <v>12227.4</v>
       </c>
       <c r="K18" s="20" t="n">
-        <v>17283.3</v>
+        <v>17695</v>
       </c>
       <c r="L18" s="11" t="n"/>
       <c r="M18" s="10" t="n"/>
@@ -6708,11 +6708,11 @@
         </is>
       </c>
       <c r="D44" s="34" t="n">
-        <v>19190</v>
+        <v>18730</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 14,190원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 18,440원)</t>
         </is>
       </c>
       <c r="G44" s="9" t="n"/>
@@ -6744,7 +6744,7 @@
       </c>
       <c r="D45" s="35" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -7404,7 +7404,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-06</t>
+          <t>UPDATE: 26-10-07</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -11219,7 +11219,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-06</t>
+          <t>UPDATE: 26-10-07</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18341,7 +18341,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -21129,7 +21129,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E3" s="43" t="n">
@@ -22660,7 +22660,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>111.96</v>
+        <v>109.28</v>
       </c>
     </row>
     <row r="32">
@@ -22670,7 +22670,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>4.03</v>
+        <v>3.93</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/217590_model.xlsx
+++ b/argus/kship/models/217590_model.xlsx
@@ -3989,7 +3989,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-07</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-08</t>
         </is>
       </c>
     </row>
@@ -7404,7 +7404,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-07</t>
+          <t>UPDATE: 26-10-08</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -11219,7 +11219,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-07</t>
+          <t>UPDATE: 26-10-08</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/217590_model.xlsx
+++ b/argus/kship/models/217590_model.xlsx
@@ -4541,35 +4541,35 @@
         <v>1418.75</v>
       </c>
       <c r="K6" s="16" t="n">
-        <v>1348.08</v>
+        <v>1346.2</v>
       </c>
       <c r="L6" s="17" t="n">
-        <v>1458.99</v>
+        <v>1458.38</v>
       </c>
       <c r="M6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="N6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="O6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="P6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="Q6" s="11" t="n"/>
       <c r="R6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="S6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="T6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="U6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="V6" s="11" t="n"/>
     </row>
@@ -4603,35 +4603,35 @@
         <v>1355.4</v>
       </c>
       <c r="K7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="L7" s="17" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="M7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="N7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="O7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="P7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="Q7" s="11" t="n"/>
       <c r="R7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="S7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="T7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="U7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="V7" s="11" t="n"/>
     </row>
@@ -4665,35 +4665,35 @@
         <v>890.41</v>
       </c>
       <c r="K8" s="16" t="n">
-        <v>853.26</v>
+        <v>851.8099999999999</v>
       </c>
       <c r="L8" s="17" t="n">
-        <v>920.3099999999999</v>
+        <v>919.9299999999999</v>
       </c>
       <c r="M8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="N8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="O8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="P8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="Q8" s="11" t="n"/>
       <c r="R8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="S8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="T8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="U8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="V8" s="11" t="n"/>
     </row>
@@ -4727,35 +4727,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="K9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="L9" s="17" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="M9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="N9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="O9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="P9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="Q9" s="11" t="n"/>
       <c r="R9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="S9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="T9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="U9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="V9" s="11" t="n"/>
     </row>
@@ -4789,35 +4789,35 @@
         <v>1631.97</v>
       </c>
       <c r="K10" s="16" t="n">
-        <v>1516.47</v>
+        <v>1512.43</v>
       </c>
       <c r="L10" s="17" t="n">
-        <v>1692.86</v>
+        <v>1691.86</v>
       </c>
       <c r="M10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="N10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="O10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="P10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="Q10" s="11" t="n"/>
       <c r="R10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="S10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="T10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="U10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="V10" s="11" t="n"/>
     </row>
@@ -4851,35 +4851,35 @@
         <v>1539.06</v>
       </c>
       <c r="K11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="L11" s="17" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="M11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="N11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="O11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="P11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="Q11" s="11" t="n"/>
       <c r="R11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="S11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="T11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="U11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="V11" s="11" t="n"/>
     </row>
@@ -4913,35 +4913,35 @@
         <v>210.43</v>
       </c>
       <c r="K12" s="16" t="n">
-        <v>201.07</v>
+        <v>200.79</v>
       </c>
       <c r="L12" s="17" t="n">
-        <v>213.96</v>
+        <v>213.89</v>
       </c>
       <c r="M12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="N12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="O12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="P12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="Q12" s="11" t="n"/>
       <c r="R12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="S12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="T12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="U12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="V12" s="11" t="n"/>
     </row>
@@ -4975,35 +4975,35 @@
         <v>202.16</v>
       </c>
       <c r="K13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="L13" s="17" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="M13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="N13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="O13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="P13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="Q13" s="11" t="n"/>
       <c r="R13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="S13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="T13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="U13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="V13" s="11" t="n"/>
     </row>
@@ -5054,7 +5054,7 @@
         <v>13570</v>
       </c>
       <c r="K15" s="20" t="n">
-        <v>18730</v>
+        <v>17990</v>
       </c>
       <c r="L15" s="11" t="n"/>
       <c r="M15" s="10" t="n"/>
@@ -5171,7 +5171,7 @@
         <v>12227.4</v>
       </c>
       <c r="K18" s="20" t="n">
-        <v>17695</v>
+        <v>17710</v>
       </c>
       <c r="L18" s="11" t="n"/>
       <c r="M18" s="10" t="n"/>
@@ -6708,11 +6708,11 @@
         </is>
       </c>
       <c r="D44" s="34" t="n">
-        <v>18730</v>
+        <v>17990</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 18,440원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 19,090원)</t>
         </is>
       </c>
       <c r="G44" s="9" t="n"/>
@@ -6744,7 +6744,7 @@
       </c>
       <c r="D45" s="35" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -18341,7 +18341,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -21129,7 +21129,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E3" s="43" t="n">
@@ -22660,7 +22660,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>109.28</v>
+        <v>104.96</v>
       </c>
     </row>
     <row r="32">
@@ -22670,7 +22670,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>3.93</v>
+        <v>3.78</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/217590_model.xlsx
+++ b/argus/kship/models/217590_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$V$1</definedName>
@@ -23,7 +23,7 @@
     <definedName name="BS연결H">BS연결!$C$1:$V$1</definedName>
     <definedName name="BS연결">BS연결!$C$5:$V$101</definedName>
     <definedName name="BS별도H">BS별도!$C$1:$V$1</definedName>
-    <definedName name="BS별도">BS별도!$C$5:$V$91</definedName>
+    <definedName name="BS별도">BS별도!$C$5:$V$92</definedName>
     <definedName name="SUBQH">subQ!$A$1:$V$1</definedName>
     <definedName name="subQ">subQ!$A$5:$V$43</definedName>
   </definedNames>
@@ -3989,7 +3989,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-08</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-09</t>
         </is>
       </c>
     </row>
@@ -4190,7 +4190,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>한계: 모델 quality.warnings — 매출 드라이버 폴백(고객 연동 격자 상관 0.92 가 단일 검정 5% 임계 r 0.95 미달(n=4) (suppliers_mentions·시차 1·수준·창 8)): 전년동기 × (1+g) 추세 / 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출 / 금융손익 실적→추정 단절: 최근 4분기 실적 +1/-2/+10/+9(중위 +5억) → 추정 2026Q3 +2억(차 -3억, -57%) — 추정은 이자손익 + 기타금융 중위, 외환·파생 평가손익 0 가정(환율 효과는 환관련손익 행). 값은 바꾸지 않음 — 지배NI·EPS 해석 시 참고</t>
+          <t>한계: 모델 quality.warnings — 매출 드라이버 폴백(고객 연동 격자 상관 0.92 가 단일 검정 5% 임계 r 0.95 미달(n=4, n_eff=4) (suppliers_mentions·시차 1·수준·창 8)): 전년동기 × (1+g) 추세 / 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출 / 금융손익 실적→추정 단절: 최근 4분기 실적 +1/-2/+10/+9(중위 +5억) → 추정 2026Q3 +2억(차 -3억, -57%) — 추정은 이자손익 + 기타금융 중위, 외환·파생 평가손익 0 가정(환율 효과는 환관련손익 행). 값은 바꾸지 않음 — 지배NI·EPS 해석 시 참고</t>
         </is>
       </c>
     </row>
@@ -7404,7 +7404,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-08</t>
+          <t>UPDATE: 26-10-09</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -11077,7 +11077,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V91"/>
+  <dimension ref="A1:V92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -11219,7 +11219,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-08</t>
+          <t>UPDATE: 26-10-09</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -12325,19 +12325,19 @@
         </is>
       </c>
       <c r="E30" s="18" t="n">
-        <v>448.08</v>
+        <v>676.63</v>
       </c>
       <c r="F30" s="18" t="n">
-        <v>388.84</v>
+        <v>623.4299999999999</v>
       </c>
       <c r="G30" s="37" t="n">
-        <v>388.84</v>
+        <v>623.4299999999999</v>
       </c>
       <c r="H30" s="18" t="n">
-        <v>339.75</v>
+        <v>659.8</v>
       </c>
       <c r="I30" s="19" t="n">
-        <v>507.37</v>
+        <v>1251.02</v>
       </c>
       <c r="J30" s="10" t="n"/>
       <c r="K30" s="10" t="n"/>
@@ -12691,23 +12691,23 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>기타비유동금융부채</t>
+          <t>비유동리스부채</t>
         </is>
       </c>
       <c r="E40" s="18" t="n">
-        <v>6</v>
+        <v>228.55</v>
       </c>
       <c r="F40" s="18" t="n">
-        <v>6</v>
+        <v>234.59</v>
       </c>
       <c r="G40" s="37" t="n">
-        <v>6</v>
+        <v>234.59</v>
       </c>
       <c r="H40" s="18" t="n">
-        <v>6</v>
+        <v>320.05</v>
       </c>
       <c r="I40" s="19" t="n">
-        <v>6</v>
+        <v>743.65</v>
       </c>
       <c r="J40" s="10" t="n"/>
       <c r="K40" s="10" t="n"/>
@@ -12733,19 +12733,19 @@
         </is>
       </c>
       <c r="E41" s="18" t="n">
-        <v>6</v>
+        <v>234.55</v>
       </c>
       <c r="F41" s="18" t="n">
-        <v>6</v>
+        <v>240.59</v>
       </c>
       <c r="G41" s="37" t="n">
-        <v>6</v>
+        <v>240.59</v>
       </c>
       <c r="H41" s="18" t="n">
-        <v>6</v>
+        <v>326.05</v>
       </c>
       <c r="I41" s="19" t="n">
-        <v>6</v>
+        <v>749.65</v>
       </c>
       <c r="J41" s="10" t="n"/>
       <c r="K41" s="10" t="n"/>
@@ -12767,23 +12767,23 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>확정급여부채</t>
+          <t>기타비유동금융부채</t>
         </is>
       </c>
       <c r="E42" s="18" t="n">
-        <v>2717.67</v>
+        <v>6</v>
       </c>
       <c r="F42" s="18" t="n">
-        <v>86.01000000000001</v>
+        <v>6</v>
       </c>
       <c r="G42" s="37" t="n">
-        <v>86.01000000000001</v>
+        <v>6</v>
       </c>
       <c r="H42" s="18" t="n">
-        <v>578.51</v>
+        <v>6</v>
       </c>
       <c r="I42" s="19" t="n">
-        <v>901.41</v>
+        <v>6</v>
       </c>
       <c r="J42" s="10" t="n"/>
       <c r="K42" s="10" t="n"/>
@@ -12805,23 +12805,23 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>장기충당부채</t>
+          <t>확정급여부채</t>
         </is>
       </c>
       <c r="E43" s="18" t="n">
-        <v>187.13</v>
+        <v>2717.67</v>
       </c>
       <c r="F43" s="18" t="n">
-        <v>242.39</v>
+        <v>86.01000000000001</v>
       </c>
       <c r="G43" s="37" t="n">
-        <v>242.39</v>
+        <v>86.01000000000001</v>
       </c>
       <c r="H43" s="18" t="n">
-        <v>45.68</v>
+        <v>578.51</v>
       </c>
       <c r="I43" s="19" t="n">
-        <v>56.17</v>
+        <v>901.41</v>
       </c>
       <c r="J43" s="10" t="n"/>
       <c r="K43" s="10" t="n"/>
@@ -12843,23 +12843,23 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>부채총계</t>
+          <t>장기충당부채</t>
         </is>
       </c>
       <c r="E44" s="18" t="n">
-        <v>107062.9</v>
+        <v>187.13</v>
       </c>
       <c r="F44" s="18" t="n">
-        <v>111325.11</v>
+        <v>242.39</v>
       </c>
       <c r="G44" s="37" t="n">
-        <v>111325.11</v>
+        <v>242.39</v>
       </c>
       <c r="H44" s="18" t="n">
-        <v>104632.48</v>
+        <v>45.68</v>
       </c>
       <c r="I44" s="19" t="n">
-        <v>102081.54</v>
+        <v>56.17</v>
       </c>
       <c r="J44" s="10" t="n"/>
       <c r="K44" s="10" t="n"/>
@@ -12881,23 +12881,23 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>자본금</t>
+          <t>부채총계</t>
         </is>
       </c>
       <c r="E45" s="18" t="n">
-        <v>1974.42</v>
+        <v>107062.9</v>
       </c>
       <c r="F45" s="18" t="n">
-        <v>2409.42</v>
+        <v>111325.11</v>
       </c>
       <c r="G45" s="37" t="n">
-        <v>2409.42</v>
+        <v>111325.11</v>
       </c>
       <c r="H45" s="18" t="n">
-        <v>2409.42</v>
+        <v>104632.48</v>
       </c>
       <c r="I45" s="19" t="n">
-        <v>2409.42</v>
+        <v>102081.54</v>
       </c>
       <c r="J45" s="10" t="n"/>
       <c r="K45" s="10" t="n"/>
@@ -12919,23 +12919,23 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>자본잉여금</t>
+          <t>자본금</t>
         </is>
       </c>
       <c r="E46" s="18" t="n">
-        <v>20054.61</v>
+        <v>1974.42</v>
       </c>
       <c r="F46" s="18" t="n">
-        <v>58192.36</v>
+        <v>2409.42</v>
       </c>
       <c r="G46" s="37" t="n">
-        <v>58192.36</v>
+        <v>2409.42</v>
       </c>
       <c r="H46" s="18" t="n">
-        <v>58192.36</v>
+        <v>2409.42</v>
       </c>
       <c r="I46" s="19" t="n">
-        <v>58192.71</v>
+        <v>2409.42</v>
       </c>
       <c r="J46" s="10" t="n"/>
       <c r="K46" s="10" t="n"/>
@@ -12957,23 +12957,23 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>기타포괄이익누계액</t>
+          <t>자본잉여금</t>
         </is>
       </c>
       <c r="E47" s="18" t="n">
-        <v>7430.19</v>
+        <v>20054.61</v>
       </c>
       <c r="F47" s="18" t="n">
-        <v>7430.19</v>
+        <v>58192.36</v>
       </c>
       <c r="G47" s="37" t="n">
-        <v>7430.19</v>
+        <v>58192.36</v>
       </c>
       <c r="H47" s="18" t="n">
-        <v>7430.19</v>
+        <v>58192.36</v>
       </c>
       <c r="I47" s="19" t="n">
-        <v>7430.19</v>
+        <v>58192.71</v>
       </c>
       <c r="J47" s="10" t="n"/>
       <c r="K47" s="10" t="n"/>
@@ -12995,23 +12995,23 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>기타자본</t>
+          <t>기타포괄이익누계액</t>
         </is>
       </c>
       <c r="E48" s="18" t="n">
-        <v>-420.46</v>
+        <v>7430.19</v>
       </c>
       <c r="F48" s="18" t="n">
-        <v>209.12</v>
+        <v>7430.19</v>
       </c>
       <c r="G48" s="37" t="n">
-        <v>209.12</v>
+        <v>7430.19</v>
       </c>
       <c r="H48" s="18" t="n">
-        <v>209.12</v>
+        <v>7430.19</v>
       </c>
       <c r="I48" s="19" t="n">
-        <v>209.12</v>
+        <v>7430.19</v>
       </c>
       <c r="J48" s="10" t="n"/>
       <c r="K48" s="10" t="n"/>
@@ -13033,23 +13033,23 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>이익잉여금</t>
+          <t>기타자본</t>
         </is>
       </c>
       <c r="E49" s="18" t="n">
-        <v>51190.05</v>
+        <v>-420.46</v>
       </c>
       <c r="F49" s="18" t="n">
-        <v>49294.84</v>
+        <v>209.12</v>
       </c>
       <c r="G49" s="37" t="n">
-        <v>49294.84</v>
+        <v>209.12</v>
       </c>
       <c r="H49" s="18" t="n">
-        <v>51656.44</v>
+        <v>209.12</v>
       </c>
       <c r="I49" s="19" t="n">
-        <v>55725.88</v>
+        <v>209.12</v>
       </c>
       <c r="J49" s="10" t="n"/>
       <c r="K49" s="10" t="n"/>
@@ -13071,23 +13071,23 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>자본총계</t>
+          <t>이익잉여금</t>
         </is>
       </c>
       <c r="E50" s="18" t="n">
-        <v>80228.81</v>
+        <v>51190.05</v>
       </c>
       <c r="F50" s="18" t="n">
-        <v>117535.94</v>
+        <v>49294.84</v>
       </c>
       <c r="G50" s="37" t="n">
-        <v>117535.94</v>
+        <v>49294.84</v>
       </c>
       <c r="H50" s="18" t="n">
-        <v>119897.54</v>
+        <v>51656.44</v>
       </c>
       <c r="I50" s="19" t="n">
-        <v>123967.32</v>
+        <v>55725.88</v>
       </c>
       <c r="J50" s="10" t="n"/>
       <c r="K50" s="10" t="n"/>
@@ -13109,23 +13109,23 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>부채와자본총계</t>
+          <t>자본총계</t>
         </is>
       </c>
       <c r="E51" s="18" t="n">
-        <v>187291.71</v>
+        <v>80228.81</v>
       </c>
       <c r="F51" s="18" t="n">
-        <v>228861.05</v>
+        <v>117535.94</v>
       </c>
       <c r="G51" s="37" t="n">
-        <v>228861.05</v>
+        <v>117535.94</v>
       </c>
       <c r="H51" s="18" t="n">
-        <v>224530.02</v>
+        <v>119897.54</v>
       </c>
       <c r="I51" s="19" t="n">
-        <v>226048.87</v>
+        <v>123967.32</v>
       </c>
       <c r="J51" s="10" t="n"/>
       <c r="K51" s="10" t="n"/>
@@ -13147,23 +13147,23 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>지배주주지분</t>
+          <t>부채와자본총계</t>
         </is>
       </c>
       <c r="E52" s="18" t="n">
-        <v>80228.81</v>
+        <v>187291.71</v>
       </c>
       <c r="F52" s="18" t="n">
-        <v>117535.94</v>
+        <v>228861.05</v>
       </c>
       <c r="G52" s="37" t="n">
-        <v>117535.94</v>
+        <v>228861.05</v>
       </c>
       <c r="H52" s="18" t="n">
-        <v>119897.54</v>
+        <v>224530.02</v>
       </c>
       <c r="I52" s="19" t="n">
-        <v>123967.32</v>
+        <v>226048.87</v>
       </c>
       <c r="J52" s="10" t="n"/>
       <c r="K52" s="10" t="n"/>
@@ -13185,23 +13185,23 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>총차입금</t>
+          <t>지배주주지분</t>
         </is>
       </c>
       <c r="E53" s="18" t="n">
-        <v>62919.38</v>
+        <v>80228.81</v>
       </c>
       <c r="F53" s="18" t="n">
-        <v>56700.55</v>
+        <v>117535.94</v>
       </c>
       <c r="G53" s="37" t="n">
-        <v>56700.55</v>
+        <v>117535.94</v>
       </c>
       <c r="H53" s="18" t="n">
-        <v>49555.9</v>
+        <v>119897.54</v>
       </c>
       <c r="I53" s="19" t="n">
-        <v>0</v>
+        <v>123967.32</v>
       </c>
       <c r="J53" s="10" t="n"/>
       <c r="K53" s="10" t="n"/>
@@ -13223,23 +13223,23 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>순차입금</t>
+          <t>총차입금</t>
         </is>
       </c>
       <c r="E54" s="18" t="n">
-        <v>58291.98</v>
+        <v>62919.38</v>
       </c>
       <c r="F54" s="18" t="n">
-        <v>47510.6</v>
+        <v>56700.55</v>
       </c>
       <c r="G54" s="37" t="n">
-        <v>47510.6</v>
+        <v>56700.55</v>
       </c>
       <c r="H54" s="18" t="n">
-        <v>47273.83</v>
+        <v>49555.9</v>
       </c>
       <c r="I54" s="19" t="n">
-        <v>-3182.25</v>
+        <v>0</v>
       </c>
       <c r="J54" s="10" t="n"/>
       <c r="K54" s="10" t="n"/>
@@ -13261,23 +13261,23 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>이자발생자산</t>
+          <t>순차입금</t>
         </is>
       </c>
       <c r="E55" s="18" t="n">
-        <v>4664.07</v>
+        <v>58291.98</v>
       </c>
       <c r="F55" s="18" t="n">
-        <v>9226.620000000001</v>
+        <v>47510.6</v>
       </c>
       <c r="G55" s="37" t="n">
-        <v>9226.620000000001</v>
+        <v>47510.6</v>
       </c>
       <c r="H55" s="18" t="n">
-        <v>2318.74</v>
+        <v>47273.83</v>
       </c>
       <c r="I55" s="19" t="n">
-        <v>3218.92</v>
+        <v>-3182.25</v>
       </c>
       <c r="J55" s="10" t="n"/>
       <c r="K55" s="10" t="n"/>
@@ -13299,20 +13299,23 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>단기투자자산(공정가치)</t>
-        </is>
+          <t>이자발생자산</t>
+        </is>
+      </c>
+      <c r="E56" s="18" t="n">
+        <v>4664.07</v>
       </c>
       <c r="F56" s="18" t="n">
-        <v>5009.77</v>
+        <v>9226.620000000001</v>
       </c>
       <c r="G56" s="37" t="n">
-        <v>5009.77</v>
+        <v>9226.620000000001</v>
       </c>
       <c r="H56" s="18" t="n">
-        <v>0</v>
+        <v>2318.74</v>
       </c>
       <c r="I56" s="19" t="n">
-        <v>0</v>
+        <v>3218.92</v>
       </c>
       <c r="J56" s="10" t="n"/>
       <c r="K56" s="10" t="n"/>
@@ -13334,19 +13337,21 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>단기금융부채(face)</t>
+          <t>단기투자자산(공정가치)</t>
         </is>
       </c>
       <c r="F57" s="18" t="n">
-        <v>44830.98</v>
+        <v>5009.77</v>
       </c>
       <c r="G57" s="37" t="n">
-        <v>44830.98</v>
+        <v>5009.77</v>
       </c>
       <c r="H57" s="18" t="n">
-        <v>38273.29</v>
-      </c>
-      <c r="I57" s="5" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="I57" s="19" t="n">
+        <v>0</v>
+      </c>
       <c r="J57" s="10" t="n"/>
       <c r="K57" s="10" t="n"/>
       <c r="L57" s="11" t="n"/>
@@ -13367,22 +13372,19 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>매출액(수익)</t>
-        </is>
-      </c>
-      <c r="E58" s="18" t="n">
-        <v>74528.07000000001</v>
+          <t>단기금융부채(face)</t>
+        </is>
       </c>
       <c r="F58" s="18" t="n">
-        <v>73781.16</v>
-      </c>
-      <c r="G58" s="9" t="n"/>
+        <v>44830.98</v>
+      </c>
+      <c r="G58" s="37" t="n">
+        <v>44830.98</v>
+      </c>
       <c r="H58" s="18" t="n">
-        <v>89557.77</v>
-      </c>
-      <c r="I58" s="19" t="n">
-        <v>100667.04</v>
-      </c>
+        <v>38273.29</v>
+      </c>
+      <c r="I58" s="5" t="n"/>
       <c r="J58" s="10" t="n"/>
       <c r="K58" s="10" t="n"/>
       <c r="L58" s="11" t="n"/>
@@ -13403,21 +13405,21 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>매출원가</t>
+          <t>매출액(수익)</t>
         </is>
       </c>
       <c r="E59" s="18" t="n">
-        <v>67811.77</v>
+        <v>74528.07000000001</v>
       </c>
       <c r="F59" s="18" t="n">
-        <v>69189.67</v>
+        <v>73781.16</v>
       </c>
       <c r="G59" s="9" t="n"/>
       <c r="H59" s="18" t="n">
-        <v>83419.89999999999</v>
+        <v>89557.77</v>
       </c>
       <c r="I59" s="19" t="n">
-        <v>92143.08</v>
+        <v>100667.04</v>
       </c>
       <c r="J59" s="10" t="n"/>
       <c r="K59" s="10" t="n"/>
@@ -13439,21 +13441,21 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>매출총이익</t>
+          <t>매출원가</t>
         </is>
       </c>
       <c r="E60" s="18" t="n">
-        <v>6716.31</v>
+        <v>67811.77</v>
       </c>
       <c r="F60" s="18" t="n">
-        <v>4591.5</v>
+        <v>69189.67</v>
       </c>
       <c r="G60" s="9" t="n"/>
       <c r="H60" s="18" t="n">
-        <v>6137.87</v>
+        <v>83419.89999999999</v>
       </c>
       <c r="I60" s="19" t="n">
-        <v>8523.959999999999</v>
+        <v>92143.08</v>
       </c>
       <c r="J60" s="10" t="n"/>
       <c r="K60" s="10" t="n"/>
@@ -13475,21 +13477,21 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>판관비</t>
+          <t>매출총이익</t>
         </is>
       </c>
       <c r="E61" s="18" t="n">
-        <v>4553.51</v>
+        <v>6716.31</v>
       </c>
       <c r="F61" s="18" t="n">
-        <v>5642.54</v>
+        <v>4591.5</v>
       </c>
       <c r="G61" s="9" t="n"/>
       <c r="H61" s="18" t="n">
-        <v>3692.09</v>
+        <v>6137.87</v>
       </c>
       <c r="I61" s="19" t="n">
-        <v>5096</v>
+        <v>8523.959999999999</v>
       </c>
       <c r="J61" s="10" t="n"/>
       <c r="K61" s="10" t="n"/>
@@ -13511,21 +13513,21 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>영업이익</t>
+          <t>판관비</t>
         </is>
       </c>
       <c r="E62" s="18" t="n">
-        <v>2162.79</v>
+        <v>4553.51</v>
       </c>
       <c r="F62" s="18" t="n">
-        <v>-1051.04</v>
+        <v>5642.54</v>
       </c>
       <c r="G62" s="9" t="n"/>
       <c r="H62" s="18" t="n">
-        <v>2445.78</v>
+        <v>3692.09</v>
       </c>
       <c r="I62" s="19" t="n">
-        <v>3427.96</v>
+        <v>5096</v>
       </c>
       <c r="J62" s="10" t="n"/>
       <c r="K62" s="10" t="n"/>
@@ -13547,21 +13549,21 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>기타영업외수익</t>
+          <t>영업이익</t>
         </is>
       </c>
       <c r="E63" s="18" t="n">
-        <v>623.38</v>
+        <v>2162.79</v>
       </c>
       <c r="F63" s="18" t="n">
-        <v>680.17</v>
+        <v>-1051.04</v>
       </c>
       <c r="G63" s="9" t="n"/>
       <c r="H63" s="18" t="n">
-        <v>1849.16</v>
+        <v>2445.78</v>
       </c>
       <c r="I63" s="19" t="n">
-        <v>1132.13</v>
+        <v>3427.96</v>
       </c>
       <c r="J63" s="10" t="n"/>
       <c r="K63" s="10" t="n"/>
@@ -13583,21 +13585,21 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>기타영업외비용</t>
+          <t>기타영업외수익</t>
         </is>
       </c>
       <c r="E64" s="18" t="n">
-        <v>-98.39</v>
+        <v>623.38</v>
       </c>
       <c r="F64" s="18" t="n">
-        <v>320.96</v>
+        <v>680.17</v>
       </c>
       <c r="G64" s="9" t="n"/>
       <c r="H64" s="18" t="n">
-        <v>1008.78</v>
+        <v>1849.16</v>
       </c>
       <c r="I64" s="19" t="n">
-        <v>539.96</v>
+        <v>1132.13</v>
       </c>
       <c r="J64" s="10" t="n"/>
       <c r="K64" s="10" t="n"/>
@@ -13619,21 +13621,21 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>금융수익</t>
+          <t>기타영업외비용</t>
         </is>
       </c>
       <c r="E65" s="18" t="n">
-        <v>1130.63</v>
+        <v>-98.39</v>
       </c>
       <c r="F65" s="18" t="n">
-        <v>1829.58</v>
+        <v>320.96</v>
       </c>
       <c r="G65" s="9" t="n"/>
       <c r="H65" s="18" t="n">
-        <v>3502.43</v>
+        <v>1008.78</v>
       </c>
       <c r="I65" s="19" t="n">
-        <v>3350.62</v>
+        <v>539.96</v>
       </c>
       <c r="J65" s="10" t="n"/>
       <c r="K65" s="10" t="n"/>
@@ -13655,21 +13657,21 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>금융비용</t>
+          <t>금융수익</t>
         </is>
       </c>
       <c r="E66" s="18" t="n">
-        <v>913.08</v>
+        <v>1130.63</v>
       </c>
       <c r="F66" s="18" t="n">
-        <v>1965.31</v>
+        <v>1829.58</v>
       </c>
       <c r="G66" s="9" t="n"/>
       <c r="H66" s="18" t="n">
-        <v>2348.01</v>
+        <v>3502.43</v>
       </c>
       <c r="I66" s="19" t="n">
-        <v>2290.12</v>
+        <v>3350.62</v>
       </c>
       <c r="J66" s="10" t="n"/>
       <c r="K66" s="10" t="n"/>
@@ -13691,21 +13693,21 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>법인세비용차감전계속사업이익</t>
+          <t>금융비용</t>
         </is>
       </c>
       <c r="E67" s="18" t="n">
-        <v>3102.12</v>
+        <v>913.08</v>
       </c>
       <c r="F67" s="18" t="n">
-        <v>-827.5700000000001</v>
+        <v>1965.31</v>
       </c>
       <c r="G67" s="9" t="n"/>
       <c r="H67" s="18" t="n">
-        <v>4440.58</v>
+        <v>2348.01</v>
       </c>
       <c r="I67" s="19" t="n">
-        <v>5080.63</v>
+        <v>2290.12</v>
       </c>
       <c r="J67" s="10" t="n"/>
       <c r="K67" s="10" t="n"/>
@@ -13727,21 +13729,21 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>법인세비용</t>
+          <t>법인세비용차감전계속사업이익</t>
         </is>
       </c>
       <c r="E68" s="18" t="n">
-        <v>396.95</v>
+        <v>3102.12</v>
       </c>
       <c r="F68" s="18" t="n">
-        <v>125.4</v>
+        <v>-827.5700000000001</v>
       </c>
       <c r="G68" s="9" t="n"/>
       <c r="H68" s="18" t="n">
-        <v>974.58</v>
+        <v>4440.58</v>
       </c>
       <c r="I68" s="19" t="n">
-        <v>1121.25</v>
+        <v>5080.63</v>
       </c>
       <c r="J68" s="10" t="n"/>
       <c r="K68" s="10" t="n"/>
@@ -13763,21 +13765,21 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>계속사업이익</t>
+          <t>법인세비용</t>
         </is>
       </c>
       <c r="E69" s="18" t="n">
-        <v>2705.17</v>
+        <v>396.95</v>
       </c>
       <c r="F69" s="18" t="n">
-        <v>-952.97</v>
+        <v>125.4</v>
       </c>
       <c r="G69" s="9" t="n"/>
       <c r="H69" s="18" t="n">
-        <v>3466</v>
+        <v>974.58</v>
       </c>
       <c r="I69" s="19" t="n">
-        <v>3959.39</v>
+        <v>1121.25</v>
       </c>
       <c r="J69" s="10" t="n"/>
       <c r="K69" s="10" t="n"/>
@@ -13799,21 +13801,21 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>중단사업이익</t>
+          <t>계속사업이익</t>
         </is>
       </c>
       <c r="E70" s="18" t="n">
-        <v>-512.8</v>
+        <v>2705.17</v>
       </c>
       <c r="F70" s="18" t="n">
-        <v>-500.44</v>
+        <v>-952.97</v>
       </c>
       <c r="G70" s="9" t="n"/>
       <c r="H70" s="18" t="n">
-        <v>0</v>
+        <v>3466</v>
       </c>
       <c r="I70" s="19" t="n">
-        <v>0</v>
+        <v>3959.39</v>
       </c>
       <c r="J70" s="10" t="n"/>
       <c r="K70" s="10" t="n"/>
@@ -13835,21 +13837,21 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>당기순이익</t>
+          <t>중단사업이익</t>
         </is>
       </c>
       <c r="E71" s="18" t="n">
-        <v>2192.36</v>
+        <v>-512.8</v>
       </c>
       <c r="F71" s="18" t="n">
-        <v>-1453.4</v>
+        <v>-500.44</v>
       </c>
       <c r="G71" s="9" t="n"/>
       <c r="H71" s="18" t="n">
-        <v>3466</v>
+        <v>0</v>
       </c>
       <c r="I71" s="19" t="n">
-        <v>3959.39</v>
+        <v>0</v>
       </c>
       <c r="J71" s="10" t="n"/>
       <c r="K71" s="10" t="n"/>
@@ -13871,21 +13873,21 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>금융손익</t>
+          <t>당기순이익</t>
         </is>
       </c>
       <c r="E72" s="18" t="n">
-        <v>217.55</v>
+        <v>2192.36</v>
       </c>
       <c r="F72" s="18" t="n">
-        <v>-135.73</v>
+        <v>-1453.4</v>
       </c>
       <c r="G72" s="9" t="n"/>
       <c r="H72" s="18" t="n">
-        <v>1154.42</v>
+        <v>3466</v>
       </c>
       <c r="I72" s="19" t="n">
-        <v>1060.5</v>
+        <v>3959.39</v>
       </c>
       <c r="J72" s="10" t="n"/>
       <c r="K72" s="10" t="n"/>
@@ -13907,21 +13909,21 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>기타영업외손익</t>
+          <t>금융손익</t>
         </is>
       </c>
       <c r="E73" s="18" t="n">
-        <v>721.77</v>
+        <v>217.55</v>
       </c>
       <c r="F73" s="18" t="n">
-        <v>359.21</v>
+        <v>-135.73</v>
       </c>
       <c r="G73" s="9" t="n"/>
       <c r="H73" s="18" t="n">
-        <v>840.38</v>
+        <v>1154.42</v>
       </c>
       <c r="I73" s="19" t="n">
-        <v>592.17</v>
+        <v>1060.5</v>
       </c>
       <c r="J73" s="10" t="n"/>
       <c r="K73" s="10" t="n"/>
@@ -13943,21 +13945,21 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>(지배주주지분)당기순이익</t>
+          <t>기타영업외손익</t>
         </is>
       </c>
       <c r="E74" s="18" t="n">
-        <v>2192.36</v>
+        <v>721.77</v>
       </c>
       <c r="F74" s="18" t="n">
-        <v>-1453.4</v>
+        <v>359.21</v>
       </c>
       <c r="G74" s="9" t="n"/>
       <c r="H74" s="18" t="n">
-        <v>3466</v>
+        <v>840.38</v>
       </c>
       <c r="I74" s="19" t="n">
-        <v>3959.39</v>
+        <v>592.17</v>
       </c>
       <c r="J74" s="10" t="n"/>
       <c r="K74" s="10" t="n"/>
@@ -13979,21 +13981,21 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>총포괄손익</t>
+          <t>(지배주주지분)당기순이익</t>
         </is>
       </c>
       <c r="E75" s="18" t="n">
-        <v>2297.58</v>
+        <v>2192.36</v>
       </c>
       <c r="F75" s="18" t="n">
-        <v>-1895.2</v>
+        <v>-1453.4</v>
       </c>
       <c r="G75" s="9" t="n"/>
       <c r="H75" s="18" t="n">
-        <v>3553.2</v>
+        <v>3466</v>
       </c>
       <c r="I75" s="19" t="n">
-        <v>4069.44</v>
+        <v>3959.39</v>
       </c>
       <c r="J75" s="10" t="n"/>
       <c r="K75" s="10" t="n"/>
@@ -14015,21 +14017,21 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>영업활동으로인한현금흐름</t>
+          <t>총포괄손익</t>
         </is>
       </c>
       <c r="E76" s="18" t="n">
-        <v>2857.58</v>
+        <v>2297.58</v>
       </c>
       <c r="F76" s="18" t="n">
-        <v>1683.89</v>
+        <v>-1895.2</v>
       </c>
       <c r="G76" s="9" t="n"/>
       <c r="H76" s="18" t="n">
-        <v>-8824.940000000001</v>
+        <v>3553.2</v>
       </c>
       <c r="I76" s="19" t="n">
-        <v>-1669.51</v>
+        <v>4069.44</v>
       </c>
       <c r="J76" s="10" t="n"/>
       <c r="K76" s="10" t="n"/>
@@ -14051,21 +14053,21 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>법인세납부(CF)</t>
+          <t>영업활동으로인한현금흐름</t>
         </is>
       </c>
       <c r="E77" s="18" t="n">
-        <v>-463.69</v>
+        <v>2857.58</v>
       </c>
       <c r="F77" s="18" t="n">
-        <v>-28.49</v>
+        <v>1683.89</v>
       </c>
       <c r="G77" s="9" t="n"/>
       <c r="H77" s="18" t="n">
-        <v>-18.37</v>
+        <v>-8824.940000000001</v>
       </c>
       <c r="I77" s="19" t="n">
-        <v>-259.35</v>
+        <v>-1669.51</v>
       </c>
       <c r="J77" s="10" t="n"/>
       <c r="K77" s="10" t="n"/>
@@ -14087,21 +14089,21 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>투자활동으로인한현금흐름</t>
+          <t>법인세납부(CF)</t>
         </is>
       </c>
       <c r="E78" s="18" t="n">
-        <v>17679.8</v>
+        <v>-463.69</v>
       </c>
       <c r="F78" s="18" t="n">
-        <v>-29560.08</v>
+        <v>-28.49</v>
       </c>
       <c r="G78" s="9" t="n"/>
       <c r="H78" s="18" t="n">
-        <v>8924.299999999999</v>
+        <v>-18.37</v>
       </c>
       <c r="I78" s="19" t="n">
-        <v>6399.69</v>
+        <v>-259.35</v>
       </c>
       <c r="J78" s="10" t="n"/>
       <c r="K78" s="10" t="n"/>
@@ -14123,21 +14125,21 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>유형자산의감소</t>
+          <t>투자활동으로인한현금흐름</t>
         </is>
       </c>
       <c r="E79" s="18" t="n">
-        <v>0</v>
+        <v>17679.8</v>
       </c>
       <c r="F79" s="18" t="n">
-        <v>8.5</v>
+        <v>-29560.08</v>
       </c>
       <c r="G79" s="9" t="n"/>
       <c r="H79" s="18" t="n">
-        <v>0</v>
+        <v>8924.299999999999</v>
       </c>
       <c r="I79" s="19" t="n">
-        <v>1.5</v>
+        <v>6399.69</v>
       </c>
       <c r="J79" s="10" t="n"/>
       <c r="K79" s="10" t="n"/>
@@ -14159,21 +14161,21 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>유형자산의증가</t>
+          <t>유형자산의감소</t>
         </is>
       </c>
       <c r="E80" s="18" t="n">
-        <v>205.82</v>
+        <v>0</v>
       </c>
       <c r="F80" s="18" t="n">
-        <v>48.15</v>
+        <v>8.5</v>
       </c>
       <c r="G80" s="9" t="n"/>
       <c r="H80" s="18" t="n">
-        <v>166.45</v>
+        <v>0</v>
       </c>
       <c r="I80" s="19" t="n">
-        <v>395.7</v>
+        <v>1.5</v>
       </c>
       <c r="J80" s="10" t="n"/>
       <c r="K80" s="10" t="n"/>
@@ -14195,21 +14197,21 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>CAPEX</t>
+          <t>유형자산의증가</t>
         </is>
       </c>
       <c r="E81" s="18" t="n">
-        <v>1465.8</v>
+        <v>205.82</v>
       </c>
       <c r="F81" s="18" t="n">
-        <v>72.18000000000001</v>
+        <v>48.15</v>
       </c>
       <c r="G81" s="9" t="n"/>
       <c r="H81" s="18" t="n">
-        <v>210.15</v>
+        <v>166.45</v>
       </c>
       <c r="I81" s="19" t="n">
-        <v>422.46</v>
+        <v>395.7</v>
       </c>
       <c r="J81" s="10" t="n"/>
       <c r="K81" s="10" t="n"/>
@@ -14231,21 +14233,21 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>무형자산의증가</t>
+          <t>CAPEX</t>
         </is>
       </c>
       <c r="E82" s="18" t="n">
-        <v>1259.98</v>
+        <v>1465.8</v>
       </c>
       <c r="F82" s="18" t="n">
-        <v>24.03</v>
+        <v>72.18000000000001</v>
       </c>
       <c r="G82" s="9" t="n"/>
       <c r="H82" s="18" t="n">
-        <v>43.7</v>
+        <v>210.15</v>
       </c>
       <c r="I82" s="19" t="n">
-        <v>26.76</v>
+        <v>422.46</v>
       </c>
       <c r="J82" s="10" t="n"/>
       <c r="K82" s="10" t="n"/>
@@ -14267,21 +14269,21 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>재무활동으로인한현금흐름</t>
+          <t>무형자산의증가</t>
         </is>
       </c>
       <c r="E83" s="18" t="n">
-        <v>-16576.05</v>
+        <v>1259.98</v>
       </c>
       <c r="F83" s="18" t="n">
-        <v>32211.22</v>
+        <v>24.03</v>
       </c>
       <c r="G83" s="9" t="n"/>
       <c r="H83" s="18" t="n">
-        <v>-7396.2</v>
+        <v>43.7</v>
       </c>
       <c r="I83" s="19" t="n">
-        <v>-4702.11</v>
+        <v>26.76</v>
       </c>
       <c r="J83" s="10" t="n"/>
       <c r="K83" s="10" t="n"/>
@@ -14303,21 +14305,21 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>단기차입금의증가</t>
+          <t>재무활동으로인한현금흐름</t>
         </is>
       </c>
       <c r="E84" s="18" t="n">
-        <v>2357.49</v>
+        <v>-16576.05</v>
       </c>
       <c r="F84" s="18" t="n">
-        <v>3170.33</v>
+        <v>32211.22</v>
       </c>
       <c r="G84" s="9" t="n"/>
       <c r="H84" s="18" t="n">
-        <v>19470.65</v>
+        <v>-7396.2</v>
       </c>
       <c r="I84" s="19" t="n">
-        <v>69177.25</v>
+        <v>-4702.11</v>
       </c>
       <c r="J84" s="10" t="n"/>
       <c r="K84" s="10" t="n"/>
@@ -14339,21 +14341,21 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>단기차입금의감소</t>
+          <t>단기차입금의증가</t>
         </is>
       </c>
       <c r="E85" s="18" t="n">
-        <v>3875.91</v>
+        <v>2357.49</v>
       </c>
       <c r="F85" s="18" t="n">
-        <v>8779.690000000001</v>
+        <v>3170.33</v>
       </c>
       <c r="G85" s="9" t="n"/>
       <c r="H85" s="18" t="n">
-        <v>26109.58</v>
+        <v>19470.65</v>
       </c>
       <c r="I85" s="19" t="n">
-        <v>71930.59</v>
+        <v>69177.25</v>
       </c>
       <c r="J85" s="10" t="n"/>
       <c r="K85" s="10" t="n"/>
@@ -14375,17 +14377,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>사채의감소</t>
+          <t>단기차입금의감소</t>
         </is>
       </c>
       <c r="E86" s="18" t="n">
-        <v>10500</v>
+        <v>3875.91</v>
       </c>
       <c r="F86" s="18" t="n">
-        <v>0</v>
+        <v>8779.690000000001</v>
       </c>
       <c r="G86" s="9" t="n"/>
-      <c r="I86" s="5" t="n"/>
+      <c r="H86" s="18" t="n">
+        <v>26109.58</v>
+      </c>
+      <c r="I86" s="19" t="n">
+        <v>71930.59</v>
+      </c>
       <c r="J86" s="10" t="n"/>
       <c r="K86" s="10" t="n"/>
       <c r="L86" s="11" t="n"/>
@@ -14406,22 +14413,17 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>리스부채의상환</t>
+          <t>사채의감소</t>
         </is>
       </c>
       <c r="E87" s="18" t="n">
-        <v>161.99</v>
+        <v>10500</v>
       </c>
       <c r="F87" s="18" t="n">
-        <v>165.19</v>
+        <v>0</v>
       </c>
       <c r="G87" s="9" t="n"/>
-      <c r="H87" s="18" t="n">
-        <v>170.32</v>
-      </c>
-      <c r="I87" s="19" t="n">
-        <v>170.56</v>
-      </c>
+      <c r="I87" s="5" t="n"/>
       <c r="J87" s="10" t="n"/>
       <c r="K87" s="10" t="n"/>
       <c r="L87" s="11" t="n"/>
@@ -14442,21 +14444,21 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>현금및현금성자산의증감</t>
+          <t>리스부채의상환</t>
         </is>
       </c>
       <c r="E88" s="18" t="n">
-        <v>3961.34</v>
+        <v>161.99</v>
       </c>
       <c r="F88" s="18" t="n">
-        <v>4335.03</v>
+        <v>165.19</v>
       </c>
       <c r="G88" s="9" t="n"/>
       <c r="H88" s="18" t="n">
-        <v>-7296.84</v>
+        <v>170.32</v>
       </c>
       <c r="I88" s="19" t="n">
-        <v>28.06</v>
+        <v>170.56</v>
       </c>
       <c r="J88" s="10" t="n"/>
       <c r="K88" s="10" t="n"/>
@@ -14478,21 +14480,21 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>기말현금및현금성자산</t>
+          <t>현금및현금성자산의증감</t>
         </is>
       </c>
       <c r="E89" s="18" t="n">
-        <v>3960.25</v>
+        <v>3961.34</v>
       </c>
       <c r="F89" s="18" t="n">
-        <v>4336.4</v>
+        <v>4335.03</v>
       </c>
       <c r="G89" s="9" t="n"/>
       <c r="H89" s="18" t="n">
-        <v>1667.91</v>
+        <v>-7296.84</v>
       </c>
       <c r="I89" s="19" t="n">
-        <v>25.5</v>
+        <v>28.06</v>
       </c>
       <c r="J89" s="10" t="n"/>
       <c r="K89" s="10" t="n"/>
@@ -14514,14 +14516,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>무형자산의감소</t>
-        </is>
+          <t>기말현금및현금성자산</t>
+        </is>
+      </c>
+      <c r="E90" s="18" t="n">
+        <v>3960.25</v>
       </c>
       <c r="F90" s="18" t="n">
-        <v>0</v>
+        <v>4336.4</v>
       </c>
       <c r="G90" s="9" t="n"/>
-      <c r="I90" s="5" t="n"/>
+      <c r="H90" s="18" t="n">
+        <v>1667.91</v>
+      </c>
+      <c r="I90" s="19" t="n">
+        <v>25.5</v>
+      </c>
       <c r="J90" s="10" t="n"/>
       <c r="K90" s="10" t="n"/>
       <c r="L90" s="11" t="n"/>
@@ -14542,19 +14552,14 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>유동성장기부채의감소</t>
+          <t>무형자산의감소</t>
         </is>
       </c>
       <c r="F91" s="18" t="n">
-        <v>586.96</v>
+        <v>0</v>
       </c>
       <c r="G91" s="9" t="n"/>
-      <c r="H91" s="18" t="n">
-        <v>586.96</v>
-      </c>
-      <c r="I91" s="19" t="n">
-        <v>586.95</v>
-      </c>
+      <c r="I91" s="5" t="n"/>
       <c r="J91" s="10" t="n"/>
       <c r="K91" s="10" t="n"/>
       <c r="L91" s="11" t="n"/>
@@ -14568,6 +14573,39 @@
       <c r="T91" s="10" t="n"/>
       <c r="U91" s="10" t="n"/>
       <c r="V91" s="11" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>1</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>유동성장기부채의감소</t>
+        </is>
+      </c>
+      <c r="F92" s="18" t="n">
+        <v>586.96</v>
+      </c>
+      <c r="G92" s="9" t="n"/>
+      <c r="H92" s="18" t="n">
+        <v>586.96</v>
+      </c>
+      <c r="I92" s="19" t="n">
+        <v>586.95</v>
+      </c>
+      <c r="J92" s="10" t="n"/>
+      <c r="K92" s="10" t="n"/>
+      <c r="L92" s="11" t="n"/>
+      <c r="M92" s="10" t="n"/>
+      <c r="N92" s="10" t="n"/>
+      <c r="O92" s="10" t="n"/>
+      <c r="P92" s="10" t="n"/>
+      <c r="Q92" s="11" t="n"/>
+      <c r="R92" s="10" t="n"/>
+      <c r="S92" s="10" t="n"/>
+      <c r="T92" s="10" t="n"/>
+      <c r="U92" s="10" t="n"/>
+      <c r="V92" s="11" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/argus/kship/models/217590_model.xlsx
+++ b/argus/kship/models/217590_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$V$1</definedName>
@@ -4541,35 +4541,35 @@
         <v>1418.75</v>
       </c>
       <c r="K6" s="16" t="n">
-        <v>1346.2</v>
+        <v>1345.74</v>
       </c>
       <c r="L6" s="17" t="n">
-        <v>1458.38</v>
+        <v>1457.79</v>
       </c>
       <c r="M6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="N6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="O6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="P6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="Q6" s="11" t="n"/>
       <c r="R6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="S6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="T6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="U6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="V6" s="11" t="n"/>
     </row>
@@ -4603,35 +4603,35 @@
         <v>1355.4</v>
       </c>
       <c r="K7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="L7" s="17" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="M7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="N7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="O7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="P7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="Q7" s="11" t="n"/>
       <c r="R7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="S7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="T7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="U7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="V7" s="11" t="n"/>
     </row>
@@ -4665,35 +4665,35 @@
         <v>890.41</v>
       </c>
       <c r="K8" s="16" t="n">
-        <v>851.8099999999999</v>
+        <v>851.3099999999999</v>
       </c>
       <c r="L8" s="17" t="n">
-        <v>919.9299999999999</v>
+        <v>919.5700000000001</v>
       </c>
       <c r="M8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="N8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="O8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="P8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="Q8" s="11" t="n"/>
       <c r="R8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="S8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="T8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="U8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="V8" s="11" t="n"/>
     </row>
@@ -4727,35 +4727,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="K9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="L9" s="17" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="M9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="N9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="O9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="P9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="Q9" s="11" t="n"/>
       <c r="R9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="S9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="T9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="U9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="V9" s="11" t="n"/>
     </row>
@@ -4789,35 +4789,35 @@
         <v>1631.97</v>
       </c>
       <c r="K10" s="16" t="n">
-        <v>1512.43</v>
+        <v>1510.82</v>
       </c>
       <c r="L10" s="17" t="n">
-        <v>1691.86</v>
+        <v>1690.9</v>
       </c>
       <c r="M10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="N10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="O10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="P10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="Q10" s="11" t="n"/>
       <c r="R10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="S10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="T10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="U10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="V10" s="11" t="n"/>
     </row>
@@ -4851,35 +4851,35 @@
         <v>1539.06</v>
       </c>
       <c r="K11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="L11" s="17" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="M11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="N11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="O11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="P11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="Q11" s="11" t="n"/>
       <c r="R11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="S11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="T11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="U11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="V11" s="11" t="n"/>
     </row>
@@ -4913,35 +4913,35 @@
         <v>210.43</v>
       </c>
       <c r="K12" s="16" t="n">
-        <v>200.79</v>
+        <v>200.73</v>
       </c>
       <c r="L12" s="17" t="n">
-        <v>213.89</v>
+        <v>213.82</v>
       </c>
       <c r="M12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="N12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="O12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="P12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="Q12" s="11" t="n"/>
       <c r="R12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="S12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="T12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="U12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="V12" s="11" t="n"/>
     </row>
@@ -4975,35 +4975,35 @@
         <v>202.16</v>
       </c>
       <c r="K13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="L13" s="17" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="M13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="N13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="O13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="P13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="Q13" s="11" t="n"/>
       <c r="R13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="S13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="T13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="U13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="V13" s="11" t="n"/>
     </row>
@@ -5054,7 +5054,7 @@
         <v>13570</v>
       </c>
       <c r="K15" s="20" t="n">
-        <v>17990</v>
+        <v>18240</v>
       </c>
       <c r="L15" s="11" t="n"/>
       <c r="M15" s="10" t="n"/>
@@ -5171,7 +5171,7 @@
         <v>12227.4</v>
       </c>
       <c r="K18" s="20" t="n">
-        <v>17710</v>
+        <v>17760</v>
       </c>
       <c r="L18" s="11" t="n"/>
       <c r="M18" s="10" t="n"/>
@@ -6708,11 +6708,11 @@
         </is>
       </c>
       <c r="D44" s="34" t="n">
-        <v>17990</v>
+        <v>18240</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 19,090원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 18,890원)</t>
         </is>
       </c>
       <c r="G44" s="9" t="n"/>
@@ -22698,7 +22698,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>104.96</v>
+        <v>106.42</v>
       </c>
     </row>
     <row r="32">
@@ -22708,7 +22708,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>3.78</v>
+        <v>3.83</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/217590_model.xlsx
+++ b/argus/kship/models/217590_model.xlsx
@@ -3989,7 +3989,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-09</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-10</t>
         </is>
       </c>
     </row>
@@ -4541,35 +4541,35 @@
         <v>1418.75</v>
       </c>
       <c r="K6" s="16" t="n">
-        <v>1345.74</v>
+        <v>1345.14</v>
       </c>
       <c r="L6" s="17" t="n">
-        <v>1457.79</v>
+        <v>1457.21</v>
       </c>
       <c r="M6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="N6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="O6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="P6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="Q6" s="11" t="n"/>
       <c r="R6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="S6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="T6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="U6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="V6" s="11" t="n"/>
     </row>
@@ -4603,35 +4603,35 @@
         <v>1355.4</v>
       </c>
       <c r="K7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="L7" s="17" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="M7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="N7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="O7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="P7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="Q7" s="11" t="n"/>
       <c r="R7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="S7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="T7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="U7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="V7" s="11" t="n"/>
     </row>
@@ -4665,35 +4665,35 @@
         <v>890.41</v>
       </c>
       <c r="K8" s="16" t="n">
-        <v>851.3099999999999</v>
+        <v>850.79</v>
       </c>
       <c r="L8" s="17" t="n">
-        <v>919.5700000000001</v>
+        <v>919.21</v>
       </c>
       <c r="M8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="N8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="O8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="P8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="Q8" s="11" t="n"/>
       <c r="R8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="S8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="T8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="U8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="V8" s="11" t="n"/>
     </row>
@@ -4727,35 +4727,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="K9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="L9" s="17" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="M9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="N9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="O9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="P9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="Q9" s="11" t="n"/>
       <c r="R9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="S9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="T9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="U9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="V9" s="11" t="n"/>
     </row>
@@ -4789,35 +4789,35 @@
         <v>1631.97</v>
       </c>
       <c r="K10" s="16" t="n">
-        <v>1510.82</v>
+        <v>1509.74</v>
       </c>
       <c r="L10" s="17" t="n">
-        <v>1690.9</v>
+        <v>1689.95</v>
       </c>
       <c r="M10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="N10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="O10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="P10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="Q10" s="11" t="n"/>
       <c r="R10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="S10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="T10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="U10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="V10" s="11" t="n"/>
     </row>
@@ -4851,35 +4851,35 @@
         <v>1539.06</v>
       </c>
       <c r="K11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="L11" s="17" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="M11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="N11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="O11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="P11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="Q11" s="11" t="n"/>
       <c r="R11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="S11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="T11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="U11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="V11" s="11" t="n"/>
     </row>
@@ -4913,35 +4913,35 @@
         <v>210.43</v>
       </c>
       <c r="K12" s="16" t="n">
-        <v>200.73</v>
+        <v>200.69</v>
       </c>
       <c r="L12" s="17" t="n">
-        <v>213.82</v>
+        <v>213.75</v>
       </c>
       <c r="M12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="N12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="O12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="P12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="Q12" s="11" t="n"/>
       <c r="R12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="S12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="T12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="U12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="V12" s="11" t="n"/>
     </row>
@@ -4975,35 +4975,35 @@
         <v>202.16</v>
       </c>
       <c r="K13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="L13" s="17" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="M13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="N13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="O13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="P13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="Q13" s="11" t="n"/>
       <c r="R13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="S13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="T13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="U13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="V13" s="11" t="n"/>
     </row>
@@ -7404,7 +7404,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-09</t>
+          <t>UPDATE: 26-10-10</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -11219,7 +11219,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-09</t>
+          <t>UPDATE: 26-10-10</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/217590_model.xlsx
+++ b/argus/kship/models/217590_model.xlsx
@@ -3989,7 +3989,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-10</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-11</t>
         </is>
       </c>
     </row>
@@ -7404,7 +7404,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-10</t>
+          <t>UPDATE: 26-10-11</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -11219,7 +11219,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-10</t>
+          <t>UPDATE: 26-10-11</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/217590_model.xlsx
+++ b/argus/kship/models/217590_model.xlsx
@@ -3989,7 +3989,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-11</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-12</t>
         </is>
       </c>
     </row>
@@ -5054,7 +5054,7 @@
         <v>13570</v>
       </c>
       <c r="K15" s="20" t="n">
-        <v>18240</v>
+        <v>16540</v>
       </c>
       <c r="L15" s="11" t="n"/>
       <c r="M15" s="10" t="n"/>
@@ -5171,7 +5171,7 @@
         <v>12227.4</v>
       </c>
       <c r="K18" s="20" t="n">
-        <v>17760</v>
+        <v>17556.7</v>
       </c>
       <c r="L18" s="11" t="n"/>
       <c r="M18" s="10" t="n"/>
@@ -6708,7 +6708,7 @@
         </is>
       </c>
       <c r="D44" s="34" t="n">
-        <v>18240</v>
+        <v>16540</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
@@ -6744,7 +6744,7 @@
       </c>
       <c r="D45" s="35" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -7404,7 +7404,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-11</t>
+          <t>UPDATE: 26-10-12</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -11219,7 +11219,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-11</t>
+          <t>UPDATE: 26-10-12</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18379,7 +18379,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -21167,7 +21167,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E3" s="43" t="n">
@@ -22698,7 +22698,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>106.42</v>
+        <v>96.5</v>
       </c>
     </row>
     <row r="32">
@@ -22708,7 +22708,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>3.83</v>
+        <v>3.47</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/217590_model.xlsx
+++ b/argus/kship/models/217590_model.xlsx
@@ -3989,7 +3989,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-12</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-13</t>
         </is>
       </c>
     </row>
@@ -4541,35 +4541,35 @@
         <v>1418.75</v>
       </c>
       <c r="K6" s="16" t="n">
-        <v>1345.14</v>
+        <v>1343.63</v>
       </c>
       <c r="L6" s="17" t="n">
-        <v>1457.21</v>
+        <v>1456.58</v>
       </c>
       <c r="M6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="N6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="O6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="P6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="Q6" s="11" t="n"/>
       <c r="R6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="S6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="T6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="U6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="V6" s="11" t="n"/>
     </row>
@@ -4603,35 +4603,35 @@
         <v>1355.4</v>
       </c>
       <c r="K7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="L7" s="17" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="M7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="N7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="O7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="P7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="Q7" s="11" t="n"/>
       <c r="R7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="S7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="T7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="U7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="V7" s="11" t="n"/>
     </row>
@@ -4665,35 +4665,35 @@
         <v>890.41</v>
       </c>
       <c r="K8" s="16" t="n">
-        <v>850.79</v>
+        <v>849.51</v>
       </c>
       <c r="L8" s="17" t="n">
-        <v>919.21</v>
+        <v>918.8099999999999</v>
       </c>
       <c r="M8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="N8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="O8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="P8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="Q8" s="11" t="n"/>
       <c r="R8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="S8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="T8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="U8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="V8" s="11" t="n"/>
     </row>
@@ -4727,35 +4727,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="K9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="L9" s="17" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="M9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="N9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="O9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="P9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="Q9" s="11" t="n"/>
       <c r="R9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="S9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="T9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="U9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="V9" s="11" t="n"/>
     </row>
@@ -4789,35 +4789,35 @@
         <v>1631.97</v>
       </c>
       <c r="K10" s="16" t="n">
-        <v>1509.74</v>
+        <v>1507.34</v>
       </c>
       <c r="L10" s="17" t="n">
-        <v>1689.95</v>
+        <v>1688.95</v>
       </c>
       <c r="M10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="N10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="O10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="P10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="Q10" s="11" t="n"/>
       <c r="R10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="S10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="T10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="U10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="V10" s="11" t="n"/>
     </row>
@@ -4851,35 +4851,35 @@
         <v>1539.06</v>
       </c>
       <c r="K11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="L11" s="17" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="M11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="N11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="O11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="P11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="Q11" s="11" t="n"/>
       <c r="R11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="S11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="T11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="U11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="V11" s="11" t="n"/>
     </row>
@@ -4913,35 +4913,35 @@
         <v>210.43</v>
       </c>
       <c r="K12" s="16" t="n">
-        <v>200.69</v>
+        <v>200.5</v>
       </c>
       <c r="L12" s="17" t="n">
-        <v>213.75</v>
+        <v>213.68</v>
       </c>
       <c r="M12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="N12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="O12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="P12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="Q12" s="11" t="n"/>
       <c r="R12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="S12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="T12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="U12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="V12" s="11" t="n"/>
     </row>
@@ -4975,35 +4975,35 @@
         <v>202.16</v>
       </c>
       <c r="K13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="L13" s="17" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="M13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="N13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="O13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="P13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="Q13" s="11" t="n"/>
       <c r="R13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="S13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="T13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="U13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="V13" s="11" t="n"/>
     </row>
@@ -5054,7 +5054,7 @@
         <v>13570</v>
       </c>
       <c r="K15" s="20" t="n">
-        <v>16540</v>
+        <v>15720</v>
       </c>
       <c r="L15" s="11" t="n"/>
       <c r="M15" s="10" t="n"/>
@@ -5171,7 +5171,7 @@
         <v>12227.4</v>
       </c>
       <c r="K18" s="20" t="n">
-        <v>17556.7</v>
+        <v>17278.6</v>
       </c>
       <c r="L18" s="11" t="n"/>
       <c r="M18" s="10" t="n"/>
@@ -6708,11 +6708,11 @@
         </is>
       </c>
       <c r="D44" s="34" t="n">
-        <v>16540</v>
+        <v>15720</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 18,890원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 18,060원)</t>
         </is>
       </c>
       <c r="G44" s="9" t="n"/>
@@ -6744,7 +6744,7 @@
       </c>
       <c r="D45" s="35" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -7404,7 +7404,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-12</t>
+          <t>UPDATE: 26-10-13</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -11219,7 +11219,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-12</t>
+          <t>UPDATE: 26-10-13</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18379,7 +18379,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -21167,7 +21167,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E3" s="43" t="n">
@@ -22698,7 +22698,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>96.5</v>
+        <v>91.72</v>
       </c>
     </row>
     <row r="32">
@@ -22708,7 +22708,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>3.47</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/217590_model.xlsx
+++ b/argus/kship/models/217590_model.xlsx
@@ -3989,7 +3989,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-13</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-14</t>
         </is>
       </c>
     </row>
@@ -4541,35 +4541,35 @@
         <v>1418.75</v>
       </c>
       <c r="K6" s="16" t="n">
-        <v>1343.63</v>
+        <v>1343.39</v>
       </c>
       <c r="L6" s="17" t="n">
-        <v>1456.58</v>
+        <v>1456.01</v>
       </c>
       <c r="M6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="N6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="O6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="P6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="Q6" s="11" t="n"/>
       <c r="R6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="S6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="T6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="U6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="V6" s="11" t="n"/>
     </row>
@@ -4603,35 +4603,35 @@
         <v>1355.4</v>
       </c>
       <c r="K7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="L7" s="17" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="M7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="N7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="O7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="P7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="Q7" s="11" t="n"/>
       <c r="R7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="S7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="T7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="U7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="V7" s="11" t="n"/>
     </row>
@@ -4665,35 +4665,35 @@
         <v>890.41</v>
       </c>
       <c r="K8" s="16" t="n">
-        <v>849.51</v>
+        <v>849.39</v>
       </c>
       <c r="L8" s="17" t="n">
-        <v>918.8099999999999</v>
+        <v>918.46</v>
       </c>
       <c r="M8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="N8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="O8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="P8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="Q8" s="11" t="n"/>
       <c r="R8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="S8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="T8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="U8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="V8" s="11" t="n"/>
     </row>
@@ -4727,35 +4727,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="K9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="L9" s="17" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="M9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="N9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="O9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="P9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="Q9" s="11" t="n"/>
       <c r="R9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="S9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="T9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="U9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="V9" s="11" t="n"/>
     </row>
@@ -4789,35 +4789,35 @@
         <v>1631.97</v>
       </c>
       <c r="K10" s="16" t="n">
-        <v>1507.34</v>
+        <v>1506.62</v>
       </c>
       <c r="L10" s="17" t="n">
-        <v>1688.95</v>
+        <v>1688.01</v>
       </c>
       <c r="M10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="N10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="O10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="P10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="Q10" s="11" t="n"/>
       <c r="R10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="S10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="T10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="U10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="V10" s="11" t="n"/>
     </row>
@@ -4851,35 +4851,35 @@
         <v>1539.06</v>
       </c>
       <c r="K11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="L11" s="17" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="M11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="N11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="O11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="P11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="Q11" s="11" t="n"/>
       <c r="R11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="S11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="T11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="U11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="V11" s="11" t="n"/>
     </row>
@@ -4913,35 +4913,35 @@
         <v>210.43</v>
       </c>
       <c r="K12" s="16" t="n">
-        <v>200.5</v>
+        <v>200.49</v>
       </c>
       <c r="L12" s="17" t="n">
-        <v>213.68</v>
+        <v>213.61</v>
       </c>
       <c r="M12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="N12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="O12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="P12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="Q12" s="11" t="n"/>
       <c r="R12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="S12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="T12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="U12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="V12" s="11" t="n"/>
     </row>
@@ -4975,35 +4975,35 @@
         <v>202.16</v>
       </c>
       <c r="K13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="L13" s="17" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="M13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="N13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="O13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="P13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="Q13" s="11" t="n"/>
       <c r="R13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="S13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="T13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="U13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="V13" s="11" t="n"/>
     </row>
@@ -5054,7 +5054,7 @@
         <v>13570</v>
       </c>
       <c r="K15" s="20" t="n">
-        <v>15720</v>
+        <v>15230</v>
       </c>
       <c r="L15" s="11" t="n"/>
       <c r="M15" s="10" t="n"/>
@@ -5171,7 +5171,7 @@
         <v>12227.4</v>
       </c>
       <c r="K18" s="20" t="n">
-        <v>17278.6</v>
+        <v>17017.5</v>
       </c>
       <c r="L18" s="11" t="n"/>
       <c r="M18" s="10" t="n"/>
@@ -6708,11 +6708,11 @@
         </is>
       </c>
       <c r="D44" s="34" t="n">
-        <v>15720</v>
+        <v>15230</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 18,060원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 16,690원)</t>
         </is>
       </c>
       <c r="G44" s="9" t="n"/>
@@ -6744,7 +6744,7 @@
       </c>
       <c r="D45" s="35" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -7404,7 +7404,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-13</t>
+          <t>UPDATE: 26-10-14</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -11219,7 +11219,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-13</t>
+          <t>UPDATE: 26-10-14</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18379,7 +18379,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -21167,7 +21167,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E3" s="43" t="n">
@@ -22698,7 +22698,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>91.72</v>
+        <v>88.86</v>
       </c>
     </row>
     <row r="32">
@@ -22708,7 +22708,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/217590_model.xlsx
+++ b/argus/kship/models/217590_model.xlsx
@@ -3989,7 +3989,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-14</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-19</t>
         </is>
       </c>
     </row>
@@ -4541,35 +4541,35 @@
         <v>1418.75</v>
       </c>
       <c r="K6" s="16" t="n">
-        <v>1343.39</v>
+        <v>1342.11</v>
       </c>
       <c r="L6" s="17" t="n">
-        <v>1456.01</v>
+        <v>1454.27</v>
       </c>
       <c r="M6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="N6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="O6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="P6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="Q6" s="11" t="n"/>
       <c r="R6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="S6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="T6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="U6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="V6" s="11" t="n"/>
     </row>
@@ -4603,35 +4603,35 @@
         <v>1355.4</v>
       </c>
       <c r="K7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="L7" s="17" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="M7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="N7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="O7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="P7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="Q7" s="11" t="n"/>
       <c r="R7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="S7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="T7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="U7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="V7" s="11" t="n"/>
     </row>
@@ -4665,35 +4665,35 @@
         <v>890.41</v>
       </c>
       <c r="K8" s="16" t="n">
-        <v>849.39</v>
+        <v>848.59</v>
       </c>
       <c r="L8" s="17" t="n">
-        <v>918.46</v>
+        <v>917.39</v>
       </c>
       <c r="M8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="N8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="O8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="P8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="Q8" s="11" t="n"/>
       <c r="R8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="S8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="T8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="U8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="V8" s="11" t="n"/>
     </row>
@@ -4727,35 +4727,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="K9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="L9" s="17" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="M9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="N9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="O9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="P9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="Q9" s="11" t="n"/>
       <c r="R9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="S9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="T9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="U9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="V9" s="11" t="n"/>
     </row>
@@ -4789,35 +4789,35 @@
         <v>1631.97</v>
       </c>
       <c r="K10" s="16" t="n">
-        <v>1506.62</v>
+        <v>1505.3</v>
       </c>
       <c r="L10" s="17" t="n">
-        <v>1688.01</v>
+        <v>1685.25</v>
       </c>
       <c r="M10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="N10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="O10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="P10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="Q10" s="11" t="n"/>
       <c r="R10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="S10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="T10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="U10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="V10" s="11" t="n"/>
     </row>
@@ -4851,35 +4851,35 @@
         <v>1539.06</v>
       </c>
       <c r="K11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="L11" s="17" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="M11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="N11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="O11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="P11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="Q11" s="11" t="n"/>
       <c r="R11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="S11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="T11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="U11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="V11" s="11" t="n"/>
     </row>
@@ -4913,35 +4913,35 @@
         <v>210.43</v>
       </c>
       <c r="K12" s="16" t="n">
-        <v>200.49</v>
+        <v>200.38</v>
       </c>
       <c r="L12" s="17" t="n">
-        <v>213.61</v>
+        <v>213.41</v>
       </c>
       <c r="M12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="N12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="O12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="P12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="Q12" s="11" t="n"/>
       <c r="R12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="S12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="T12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="U12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="V12" s="11" t="n"/>
     </row>
@@ -4975,35 +4975,35 @@
         <v>202.16</v>
       </c>
       <c r="K13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="L13" s="17" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="M13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="N13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="O13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="P13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="Q13" s="11" t="n"/>
       <c r="R13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="S13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="T13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="U13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="V13" s="11" t="n"/>
     </row>
@@ -5054,7 +5054,7 @@
         <v>13570</v>
       </c>
       <c r="K15" s="20" t="n">
-        <v>15230</v>
+        <v>13620</v>
       </c>
       <c r="L15" s="11" t="n"/>
       <c r="M15" s="10" t="n"/>
@@ -5132,7 +5132,7 @@
         <v>8820</v>
       </c>
       <c r="K17" s="20" t="n">
-        <v>13410</v>
+        <v>12700</v>
       </c>
       <c r="L17" s="11" t="n"/>
       <c r="M17" s="10" t="n"/>
@@ -5171,7 +5171,7 @@
         <v>12227.4</v>
       </c>
       <c r="K18" s="20" t="n">
-        <v>17017.5</v>
+        <v>16029.1</v>
       </c>
       <c r="L18" s="11" t="n"/>
       <c r="M18" s="10" t="n"/>
@@ -6708,11 +6708,11 @@
         </is>
       </c>
       <c r="D44" s="34" t="n">
-        <v>15230</v>
+        <v>13620</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 16,690원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 13,450원)</t>
         </is>
       </c>
       <c r="G44" s="9" t="n"/>
@@ -6744,7 +6744,7 @@
       </c>
       <c r="D45" s="35" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -7404,7 +7404,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-14</t>
+          <t>UPDATE: 26-10-19</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -11219,7 +11219,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-14</t>
+          <t>UPDATE: 26-10-19</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18379,7 +18379,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -21167,7 +21167,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E3" s="43" t="n">
@@ -22698,7 +22698,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>88.86</v>
+        <v>79.45999999999999</v>
       </c>
     </row>
     <row r="32">
@@ -22708,7 +22708,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>3.2</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/217590_model.xlsx
+++ b/argus/kship/models/217590_model.xlsx
@@ -3989,7 +3989,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-19</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-26</t>
         </is>
       </c>
     </row>
@@ -4541,35 +4541,35 @@
         <v>1418.75</v>
       </c>
       <c r="K6" s="16" t="n">
-        <v>1342.11</v>
+        <v>1337.49</v>
       </c>
       <c r="L6" s="17" t="n">
-        <v>1454.27</v>
+        <v>1451.19</v>
       </c>
       <c r="M6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="N6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="O6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="P6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="Q6" s="11" t="n"/>
       <c r="R6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="S6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="T6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="U6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="V6" s="11" t="n"/>
     </row>
@@ -4603,35 +4603,35 @@
         <v>1355.4</v>
       </c>
       <c r="K7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="L7" s="17" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="M7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="N7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="O7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="P7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="Q7" s="11" t="n"/>
       <c r="R7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="S7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="T7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="U7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="V7" s="11" t="n"/>
     </row>
@@ -4665,35 +4665,35 @@
         <v>890.41</v>
       </c>
       <c r="K8" s="16" t="n">
-        <v>848.59</v>
+        <v>846.51</v>
       </c>
       <c r="L8" s="17" t="n">
-        <v>917.39</v>
+        <v>915.5700000000001</v>
       </c>
       <c r="M8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="N8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="O8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="P8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="Q8" s="11" t="n"/>
       <c r="R8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="S8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="T8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="U8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="V8" s="11" t="n"/>
     </row>
@@ -4727,35 +4727,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="K9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="L9" s="17" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="M9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="N9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="O9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="P9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="Q9" s="11" t="n"/>
       <c r="R9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="S9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="T9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="U9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="V9" s="11" t="n"/>
     </row>
@@ -4789,35 +4789,35 @@
         <v>1631.97</v>
       </c>
       <c r="K10" s="16" t="n">
-        <v>1505.3</v>
+        <v>1500.06</v>
       </c>
       <c r="L10" s="17" t="n">
-        <v>1685.25</v>
+        <v>1680.5</v>
       </c>
       <c r="M10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="N10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="O10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="P10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="Q10" s="11" t="n"/>
       <c r="R10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="S10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="T10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="U10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="V10" s="11" t="n"/>
     </row>
@@ -4851,35 +4851,35 @@
         <v>1539.06</v>
       </c>
       <c r="K11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="L11" s="17" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="M11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="N11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="O11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="P11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="Q11" s="11" t="n"/>
       <c r="R11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="S11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="T11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="U11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="V11" s="11" t="n"/>
     </row>
@@ -4913,35 +4913,35 @@
         <v>210.43</v>
       </c>
       <c r="K12" s="16" t="n">
-        <v>200.38</v>
+        <v>199.88</v>
       </c>
       <c r="L12" s="17" t="n">
-        <v>213.41</v>
+        <v>213.06</v>
       </c>
       <c r="M12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="N12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="O12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="P12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="Q12" s="11" t="n"/>
       <c r="R12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="S12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="T12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="U12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="V12" s="11" t="n"/>
     </row>
@@ -4975,35 +4975,35 @@
         <v>202.16</v>
       </c>
       <c r="K13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="L13" s="17" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="M13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="N13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="O13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="P13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="Q13" s="11" t="n"/>
       <c r="R13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="S13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="T13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="U13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="V13" s="11" t="n"/>
     </row>
@@ -5054,7 +5054,7 @@
         <v>13570</v>
       </c>
       <c r="K15" s="20" t="n">
-        <v>13620</v>
+        <v>10810</v>
       </c>
       <c r="L15" s="11" t="n"/>
       <c r="M15" s="10" t="n"/>
@@ -5132,7 +5132,7 @@
         <v>8820</v>
       </c>
       <c r="K17" s="20" t="n">
-        <v>12700</v>
+        <v>10700</v>
       </c>
       <c r="L17" s="11" t="n"/>
       <c r="M17" s="10" t="n"/>
@@ -5171,7 +5171,7 @@
         <v>12227.4</v>
       </c>
       <c r="K18" s="20" t="n">
-        <v>16029.1</v>
+        <v>14712.5</v>
       </c>
       <c r="L18" s="11" t="n"/>
       <c r="M18" s="10" t="n"/>
@@ -6708,11 +6708,11 @@
         </is>
       </c>
       <c r="D44" s="34" t="n">
-        <v>13620</v>
+        <v>10810</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 13,450원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 11,660원)</t>
         </is>
       </c>
       <c r="G44" s="9" t="n"/>
@@ -6744,7 +6744,7 @@
       </c>
       <c r="D45" s="35" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -7404,7 +7404,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-19</t>
+          <t>UPDATE: 26-10-26</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -11219,7 +11219,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-19</t>
+          <t>UPDATE: 26-10-26</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18379,7 +18379,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -21167,7 +21167,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E3" s="43" t="n">
@@ -22698,7 +22698,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>79.45999999999999</v>
+        <v>63.07</v>
       </c>
     </row>
     <row r="32">
@@ -22708,7 +22708,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>2.86</v>
+        <v>2.27</v>
       </c>
     </row>
     <row r="33">
